--- a/030-試験/納品物/031-単体試験計画書兼結果書/031-単体試験計画書兼結果書（SearchResultService） - 修正ver2.xlsx
+++ b/030-試験/納品物/031-単体試験計画書兼結果書/031-単体試験計画書兼結果書（SearchResultService） - 修正ver2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\030-試験\納品物\031-単体試験計画書兼結果書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A406D6E-2400-466D-9373-6DE175A24BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C99CDA2-06D0-48D6-BE15-4ED7754FE5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{D6B31EA4-799A-4C8F-8752-A3EFBFF145C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D6B31EA4-799A-4C8F-8752-A3EFBFF145C0}"/>
   </bookViews>
   <sheets>
     <sheet name="単体試験_前提条件" sheetId="3" r:id="rId1"/>
@@ -1285,7 +1285,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1384,13 +1384,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="ＭＳ ゴシック"/>
@@ -1406,26 +1399,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="9"/>
       <name val="ＭＳ ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1861,11 +1845,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2064,7 +2048,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="13" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2073,7 +2057,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="13" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
@@ -2115,76 +2099,52 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2205,118 +2165,97 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2352,26 +2291,20 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2388,44 +2321,82 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2753,130 +2724,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="17.25" customHeight="1" thickTop="1">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="115" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="139" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="U1" s="139"/>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139"/>
-      <c r="Y1" s="139"/>
-      <c r="Z1" s="139"/>
-      <c r="AA1" s="140"/>
-      <c r="AB1" s="140"/>
-      <c r="AC1" s="140"/>
-      <c r="AD1" s="140"/>
-      <c r="AE1" s="140"/>
-      <c r="AF1" s="140"/>
-      <c r="AG1" s="140"/>
-      <c r="AH1" s="140"/>
-      <c r="AI1" s="140"/>
-      <c r="AJ1" s="140"/>
-      <c r="AK1" s="139" t="s">
+      <c r="U1" s="175"/>
+      <c r="V1" s="175"/>
+      <c r="W1" s="175"/>
+      <c r="X1" s="175"/>
+      <c r="Y1" s="175"/>
+      <c r="Z1" s="175"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
+      <c r="AC1" s="114"/>
+      <c r="AD1" s="114"/>
+      <c r="AE1" s="114"/>
+      <c r="AF1" s="114"/>
+      <c r="AG1" s="114"/>
+      <c r="AH1" s="114"/>
+      <c r="AI1" s="114"/>
+      <c r="AJ1" s="114"/>
+      <c r="AK1" s="175" t="s">
         <v>1</v>
       </c>
-      <c r="AL1" s="139"/>
-      <c r="AM1" s="139"/>
-      <c r="AN1" s="139"/>
-      <c r="AO1" s="209">
+      <c r="AL1" s="175"/>
+      <c r="AM1" s="175"/>
+      <c r="AN1" s="175"/>
+      <c r="AO1" s="108">
         <v>45595</v>
       </c>
-      <c r="AP1" s="211"/>
-      <c r="AQ1" s="211"/>
-      <c r="AR1" s="211"/>
-      <c r="AS1" s="211"/>
-      <c r="AT1" s="210"/>
-      <c r="AU1" s="150" t="s">
+      <c r="AP1" s="109"/>
+      <c r="AQ1" s="109"/>
+      <c r="AR1" s="109"/>
+      <c r="AS1" s="109"/>
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="AV1" s="151"/>
-      <c r="AW1" s="141"/>
-      <c r="AX1" s="142"/>
-      <c r="AY1" s="142"/>
-      <c r="AZ1" s="143"/>
+      <c r="AV1" s="177"/>
+      <c r="AW1" s="101"/>
+      <c r="AX1" s="102"/>
+      <c r="AY1" s="102"/>
+      <c r="AZ1" s="103"/>
     </row>
     <row r="2" spans="1:60" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A2" s="136"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="137"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="147" t="s">
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
+      <c r="P2" s="119"/>
+      <c r="Q2" s="119"/>
+      <c r="R2" s="119"/>
+      <c r="S2" s="120"/>
+      <c r="T2" s="178" t="s">
         <v>3</v>
       </c>
-      <c r="U2" s="147"/>
-      <c r="V2" s="147"/>
-      <c r="W2" s="147"/>
-      <c r="X2" s="147"/>
-      <c r="Y2" s="147"/>
-      <c r="Z2" s="147"/>
-      <c r="AA2" s="148" t="s">
+      <c r="U2" s="178"/>
+      <c r="V2" s="178"/>
+      <c r="W2" s="178"/>
+      <c r="X2" s="178"/>
+      <c r="Y2" s="178"/>
+      <c r="Z2" s="178"/>
+      <c r="AA2" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="148"/>
-      <c r="AC2" s="148"/>
-      <c r="AD2" s="148"/>
-      <c r="AE2" s="148"/>
-      <c r="AF2" s="148"/>
-      <c r="AG2" s="148"/>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="148"/>
-      <c r="AJ2" s="148"/>
-      <c r="AK2" s="147" t="s">
+      <c r="AB2" s="107"/>
+      <c r="AC2" s="107"/>
+      <c r="AD2" s="107"/>
+      <c r="AE2" s="107"/>
+      <c r="AF2" s="107"/>
+      <c r="AG2" s="107"/>
+      <c r="AH2" s="107"/>
+      <c r="AI2" s="107"/>
+      <c r="AJ2" s="107"/>
+      <c r="AK2" s="178" t="s">
         <v>5</v>
       </c>
-      <c r="AL2" s="147"/>
-      <c r="AM2" s="147"/>
-      <c r="AN2" s="147"/>
-      <c r="AO2" s="200" t="s">
+      <c r="AL2" s="178"/>
+      <c r="AM2" s="178"/>
+      <c r="AN2" s="178"/>
+      <c r="AO2" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="AP2" s="212"/>
-      <c r="AQ2" s="212"/>
-      <c r="AR2" s="212"/>
-      <c r="AS2" s="212"/>
-      <c r="AT2" s="201"/>
-      <c r="AU2" s="152"/>
-      <c r="AV2" s="153"/>
-      <c r="AW2" s="144"/>
-      <c r="AX2" s="145"/>
-      <c r="AY2" s="145"/>
-      <c r="AZ2" s="146"/>
+      <c r="AP2" s="112"/>
+      <c r="AQ2" s="112"/>
+      <c r="AR2" s="112"/>
+      <c r="AS2" s="112"/>
+      <c r="AT2" s="113"/>
+      <c r="AU2" s="179"/>
+      <c r="AV2" s="180"/>
+      <c r="AW2" s="104"/>
+      <c r="AX2" s="105"/>
+      <c r="AY2" s="105"/>
+      <c r="AZ2" s="106"/>
     </row>
     <row r="3" spans="1:60" ht="17.25" customHeight="1" thickTop="1">
       <c r="B3" s="35"/>
@@ -2940,77 +2911,77 @@
       <c r="BH3" s="35"/>
     </row>
     <row r="5" spans="1:60" ht="17.25" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="181" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="125"/>
-      <c r="C5" s="125"/>
-      <c r="D5" s="125"/>
-      <c r="E5" s="127" t="s">
+      <c r="B5" s="181"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="182" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="128"/>
-      <c r="T5" s="128"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="128"/>
-      <c r="W5" s="128"/>
-      <c r="X5" s="128"/>
-      <c r="Y5" s="128"/>
-      <c r="Z5" s="128"/>
-      <c r="AA5" s="128"/>
-      <c r="AB5" s="128"/>
-      <c r="AC5" s="128"/>
-      <c r="AD5" s="128"/>
-      <c r="AE5" s="129"/>
+      <c r="F5" s="183"/>
+      <c r="G5" s="183"/>
+      <c r="H5" s="183"/>
+      <c r="I5" s="183"/>
+      <c r="J5" s="183"/>
+      <c r="K5" s="183"/>
+      <c r="L5" s="183"/>
+      <c r="M5" s="183"/>
+      <c r="N5" s="183"/>
+      <c r="O5" s="183"/>
+      <c r="P5" s="183"/>
+      <c r="Q5" s="183"/>
+      <c r="R5" s="183"/>
+      <c r="S5" s="183"/>
+      <c r="T5" s="183"/>
+      <c r="U5" s="183"/>
+      <c r="V5" s="183"/>
+      <c r="W5" s="183"/>
+      <c r="X5" s="183"/>
+      <c r="Y5" s="183"/>
+      <c r="Z5" s="183"/>
+      <c r="AA5" s="183"/>
+      <c r="AB5" s="183"/>
+      <c r="AC5" s="183"/>
+      <c r="AD5" s="183"/>
+      <c r="AE5" s="184"/>
     </row>
     <row r="6" spans="1:60" ht="17.25" customHeight="1">
-      <c r="A6" s="126"/>
-      <c r="B6" s="126"/>
-      <c r="C6" s="126"/>
-      <c r="D6" s="126"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="131"/>
-      <c r="G6" s="131"/>
-      <c r="H6" s="131"/>
-      <c r="I6" s="131"/>
-      <c r="J6" s="131"/>
-      <c r="K6" s="131"/>
-      <c r="L6" s="131"/>
-      <c r="M6" s="131"/>
-      <c r="N6" s="131"/>
-      <c r="O6" s="131"/>
-      <c r="P6" s="131"/>
-      <c r="Q6" s="131"/>
-      <c r="R6" s="131"/>
-      <c r="S6" s="131"/>
-      <c r="T6" s="131"/>
-      <c r="U6" s="131"/>
-      <c r="V6" s="131"/>
-      <c r="W6" s="131"/>
-      <c r="X6" s="131"/>
-      <c r="Y6" s="131"/>
-      <c r="Z6" s="131"/>
-      <c r="AA6" s="131"/>
-      <c r="AB6" s="131"/>
-      <c r="AC6" s="131"/>
-      <c r="AD6" s="131"/>
-      <c r="AE6" s="132"/>
+      <c r="A6" s="185"/>
+      <c r="B6" s="185"/>
+      <c r="C6" s="185"/>
+      <c r="D6" s="185"/>
+      <c r="E6" s="186"/>
+      <c r="F6" s="187"/>
+      <c r="G6" s="187"/>
+      <c r="H6" s="187"/>
+      <c r="I6" s="187"/>
+      <c r="J6" s="187"/>
+      <c r="K6" s="187"/>
+      <c r="L6" s="187"/>
+      <c r="M6" s="187"/>
+      <c r="N6" s="187"/>
+      <c r="O6" s="187"/>
+      <c r="P6" s="187"/>
+      <c r="Q6" s="187"/>
+      <c r="R6" s="187"/>
+      <c r="S6" s="187"/>
+      <c r="T6" s="187"/>
+      <c r="U6" s="187"/>
+      <c r="V6" s="187"/>
+      <c r="W6" s="187"/>
+      <c r="X6" s="187"/>
+      <c r="Y6" s="187"/>
+      <c r="Z6" s="187"/>
+      <c r="AA6" s="187"/>
+      <c r="AB6" s="187"/>
+      <c r="AC6" s="187"/>
+      <c r="AD6" s="187"/>
+      <c r="AE6" s="188"/>
     </row>
     <row r="7" spans="1:60" ht="17.25" customHeight="1">
-      <c r="A7" s="124">
+      <c r="A7" s="100">
         <v>1</v>
       </c>
       <c r="B7" s="68"/>
@@ -3254,40 +3225,40 @@
       <c r="AD13" s="68"/>
       <c r="AE13" s="63"/>
     </row>
-    <row r="14" spans="1:60" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A14" s="103"/>
-      <c r="B14" s="104"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="106" t="s">
+    <row r="14" spans="1:60" ht="17.25" customHeight="1">
+      <c r="A14" s="70"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="65" t="s">
         <v>179</v>
       </c>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
-      <c r="M14" s="104"/>
-      <c r="N14" s="104"/>
-      <c r="O14" s="104"/>
-      <c r="P14" s="104"/>
-      <c r="Q14" s="104"/>
-      <c r="R14" s="104"/>
-      <c r="S14" s="104"/>
-      <c r="T14" s="104"/>
-      <c r="U14" s="104"/>
-      <c r="V14" s="104"/>
-      <c r="W14" s="104"/>
-      <c r="X14" s="104"/>
-      <c r="Y14" s="104"/>
-      <c r="Z14" s="104"/>
-      <c r="AA14" s="104"/>
-      <c r="AB14" s="104"/>
-      <c r="AC14" s="104"/>
-      <c r="AD14" s="104"/>
-      <c r="AE14" s="105"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="66"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="66"/>
+      <c r="X14" s="66"/>
+      <c r="Y14" s="66"/>
+      <c r="Z14" s="66"/>
+      <c r="AA14" s="66"/>
+      <c r="AB14" s="66"/>
+      <c r="AC14" s="66"/>
+      <c r="AD14" s="66"/>
+      <c r="AE14" s="67"/>
     </row>
     <row r="15" spans="1:60" ht="17.25" customHeight="1">
       <c r="A15" s="69">
@@ -3438,40 +3409,40 @@
       </c>
       <c r="AE19" s="63"/>
     </row>
-    <row r="20" spans="1:32" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A20" s="103"/>
-      <c r="B20" s="104"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="106" t="s">
+    <row r="20" spans="1:32" ht="17.25" customHeight="1">
+      <c r="A20" s="70"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="65" t="s">
         <v>180</v>
       </c>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="104"/>
-      <c r="O20" s="104"/>
-      <c r="P20" s="104"/>
-      <c r="Q20" s="104"/>
-      <c r="R20" s="104"/>
-      <c r="S20" s="104"/>
-      <c r="T20" s="104"/>
-      <c r="U20" s="104"/>
-      <c r="V20" s="104"/>
-      <c r="W20" s="104"/>
-      <c r="X20" s="104"/>
-      <c r="Y20" s="104"/>
-      <c r="Z20" s="104"/>
-      <c r="AA20" s="104"/>
-      <c r="AB20" s="104"/>
-      <c r="AC20" s="104"/>
-      <c r="AD20" s="104"/>
-      <c r="AE20" s="105"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="66"/>
+      <c r="K20" s="66"/>
+      <c r="L20" s="66"/>
+      <c r="M20" s="66"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="66"/>
+      <c r="P20" s="66"/>
+      <c r="Q20" s="66"/>
+      <c r="R20" s="66"/>
+      <c r="S20" s="66"/>
+      <c r="T20" s="66"/>
+      <c r="U20" s="66"/>
+      <c r="V20" s="66"/>
+      <c r="W20" s="66"/>
+      <c r="X20" s="66"/>
+      <c r="Y20" s="66"/>
+      <c r="Z20" s="66"/>
+      <c r="AA20" s="66"/>
+      <c r="AB20" s="66"/>
+      <c r="AC20" s="66"/>
+      <c r="AD20" s="66"/>
+      <c r="AE20" s="67"/>
     </row>
     <row r="21" spans="1:32" ht="17.25" customHeight="1">
       <c r="A21" s="69">
@@ -3568,40 +3539,40 @@
       <c r="AD25" s="68"/>
       <c r="AE25" s="63"/>
     </row>
-    <row r="26" spans="1:32" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A26" s="103"/>
-      <c r="B26" s="104"/>
-      <c r="C26" s="104"/>
-      <c r="D26" s="105"/>
-      <c r="E26" s="106" t="s">
+    <row r="26" spans="1:32" ht="17.25" customHeight="1">
+      <c r="A26" s="70"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="65" t="s">
         <v>181</v>
       </c>
-      <c r="F26" s="104"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="104"/>
-      <c r="I26" s="104"/>
-      <c r="J26" s="104"/>
-      <c r="K26" s="104"/>
-      <c r="L26" s="104"/>
-      <c r="M26" s="104"/>
-      <c r="N26" s="104"/>
-      <c r="O26" s="104"/>
-      <c r="P26" s="104"/>
-      <c r="Q26" s="104"/>
-      <c r="R26" s="104"/>
-      <c r="S26" s="104"/>
-      <c r="T26" s="104"/>
-      <c r="U26" s="104"/>
-      <c r="V26" s="104"/>
-      <c r="W26" s="104"/>
-      <c r="X26" s="104"/>
-      <c r="Y26" s="104"/>
-      <c r="Z26" s="104"/>
-      <c r="AA26" s="104"/>
-      <c r="AB26" s="104"/>
-      <c r="AC26" s="104"/>
-      <c r="AD26" s="104"/>
-      <c r="AE26" s="105"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="66"/>
+      <c r="K26" s="66"/>
+      <c r="L26" s="66"/>
+      <c r="M26" s="66"/>
+      <c r="N26" s="66"/>
+      <c r="O26" s="66"/>
+      <c r="P26" s="66"/>
+      <c r="Q26" s="66"/>
+      <c r="R26" s="66"/>
+      <c r="S26" s="66"/>
+      <c r="T26" s="66"/>
+      <c r="U26" s="66"/>
+      <c r="V26" s="66"/>
+      <c r="W26" s="66"/>
+      <c r="X26" s="66"/>
+      <c r="Y26" s="66"/>
+      <c r="Z26" s="66"/>
+      <c r="AA26" s="66"/>
+      <c r="AB26" s="66"/>
+      <c r="AC26" s="66"/>
+      <c r="AD26" s="66"/>
+      <c r="AE26" s="67"/>
     </row>
     <row r="27" spans="1:32" ht="17.25" customHeight="1">
       <c r="A27" s="69">
@@ -3699,40 +3670,40 @@
       <c r="AD31" s="68"/>
       <c r="AE31" s="63"/>
     </row>
-    <row r="32" spans="1:32" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A32" s="103"/>
-      <c r="B32" s="104"/>
-      <c r="C32" s="104"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="106" t="s">
+    <row r="32" spans="1:32" ht="17.25" customHeight="1">
+      <c r="A32" s="70"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="66"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="65" t="s">
         <v>182</v>
       </c>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="104"/>
-      <c r="N32" s="104"/>
-      <c r="O32" s="104"/>
-      <c r="P32" s="104"/>
-      <c r="Q32" s="104"/>
-      <c r="R32" s="104"/>
-      <c r="S32" s="104"/>
-      <c r="T32" s="104"/>
-      <c r="U32" s="104"/>
-      <c r="V32" s="104"/>
-      <c r="W32" s="104"/>
-      <c r="X32" s="104"/>
-      <c r="Y32" s="104"/>
-      <c r="Z32" s="104"/>
-      <c r="AA32" s="104"/>
-      <c r="AB32" s="104"/>
-      <c r="AC32" s="104"/>
-      <c r="AD32" s="104"/>
-      <c r="AE32" s="105"/>
+      <c r="F32" s="66"/>
+      <c r="G32" s="66"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="66"/>
+      <c r="J32" s="66"/>
+      <c r="K32" s="66"/>
+      <c r="L32" s="66"/>
+      <c r="M32" s="66"/>
+      <c r="N32" s="66"/>
+      <c r="O32" s="66"/>
+      <c r="P32" s="66"/>
+      <c r="Q32" s="66"/>
+      <c r="R32" s="66"/>
+      <c r="S32" s="66"/>
+      <c r="T32" s="66"/>
+      <c r="U32" s="66"/>
+      <c r="V32" s="66"/>
+      <c r="W32" s="66"/>
+      <c r="X32" s="66"/>
+      <c r="Y32" s="66"/>
+      <c r="Z32" s="66"/>
+      <c r="AA32" s="66"/>
+      <c r="AB32" s="66"/>
+      <c r="AC32" s="66"/>
+      <c r="AD32" s="66"/>
+      <c r="AE32" s="67"/>
     </row>
     <row r="33" spans="1:31" ht="17.25" customHeight="1">
       <c r="A33" s="69">
@@ -3829,40 +3800,40 @@
       <c r="AD37" s="68"/>
       <c r="AE37" s="63"/>
     </row>
-    <row r="38" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A38" s="103"/>
-      <c r="B38" s="104"/>
-      <c r="C38" s="104"/>
-      <c r="D38" s="105"/>
-      <c r="E38" s="106" t="s">
+    <row r="38" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A38" s="70"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="65" t="s">
         <v>183</v>
       </c>
-      <c r="F38" s="104"/>
-      <c r="G38" s="104"/>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="104"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="104"/>
-      <c r="M38" s="104"/>
-      <c r="N38" s="104"/>
-      <c r="O38" s="104"/>
-      <c r="P38" s="104"/>
-      <c r="Q38" s="104"/>
-      <c r="R38" s="104"/>
-      <c r="S38" s="104"/>
-      <c r="T38" s="104"/>
-      <c r="U38" s="104"/>
-      <c r="V38" s="104"/>
-      <c r="W38" s="104"/>
-      <c r="X38" s="104"/>
-      <c r="Y38" s="104"/>
-      <c r="Z38" s="104"/>
-      <c r="AA38" s="104"/>
-      <c r="AB38" s="104"/>
-      <c r="AC38" s="104"/>
-      <c r="AD38" s="104"/>
-      <c r="AE38" s="105"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="66"/>
+      <c r="J38" s="66"/>
+      <c r="K38" s="66"/>
+      <c r="L38" s="66"/>
+      <c r="M38" s="66"/>
+      <c r="N38" s="66"/>
+      <c r="O38" s="66"/>
+      <c r="P38" s="66"/>
+      <c r="Q38" s="66"/>
+      <c r="R38" s="66"/>
+      <c r="S38" s="66"/>
+      <c r="T38" s="66"/>
+      <c r="U38" s="66"/>
+      <c r="V38" s="66"/>
+      <c r="W38" s="66"/>
+      <c r="X38" s="66"/>
+      <c r="Y38" s="66"/>
+      <c r="Z38" s="66"/>
+      <c r="AA38" s="66"/>
+      <c r="AB38" s="66"/>
+      <c r="AC38" s="66"/>
+      <c r="AD38" s="66"/>
+      <c r="AE38" s="67"/>
     </row>
     <row r="39" spans="1:31" ht="17.25" customHeight="1">
       <c r="A39" s="69">
@@ -3959,40 +3930,40 @@
       <c r="AD43" s="68"/>
       <c r="AE43" s="63"/>
     </row>
-    <row r="44" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A44" s="103"/>
-      <c r="B44" s="104"/>
-      <c r="C44" s="104"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="106" t="s">
+    <row r="44" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A44" s="70"/>
+      <c r="B44" s="66"/>
+      <c r="C44" s="66"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="65" t="s">
         <v>181</v>
       </c>
-      <c r="F44" s="104"/>
-      <c r="G44" s="104"/>
-      <c r="H44" s="104"/>
-      <c r="I44" s="104"/>
-      <c r="J44" s="104"/>
-      <c r="K44" s="104"/>
-      <c r="L44" s="104"/>
-      <c r="M44" s="104"/>
-      <c r="N44" s="104"/>
-      <c r="O44" s="104"/>
-      <c r="P44" s="104"/>
-      <c r="Q44" s="104"/>
-      <c r="R44" s="104"/>
-      <c r="S44" s="104"/>
-      <c r="T44" s="104"/>
-      <c r="U44" s="104"/>
-      <c r="V44" s="104"/>
-      <c r="W44" s="104"/>
-      <c r="X44" s="104"/>
-      <c r="Y44" s="104"/>
-      <c r="Z44" s="104"/>
-      <c r="AA44" s="104"/>
-      <c r="AB44" s="104"/>
-      <c r="AC44" s="104"/>
-      <c r="AD44" s="104"/>
-      <c r="AE44" s="105"/>
+      <c r="F44" s="66"/>
+      <c r="G44" s="66"/>
+      <c r="H44" s="66"/>
+      <c r="I44" s="66"/>
+      <c r="J44" s="66"/>
+      <c r="K44" s="66"/>
+      <c r="L44" s="66"/>
+      <c r="M44" s="66"/>
+      <c r="N44" s="66"/>
+      <c r="O44" s="66"/>
+      <c r="P44" s="66"/>
+      <c r="Q44" s="66"/>
+      <c r="R44" s="66"/>
+      <c r="S44" s="66"/>
+      <c r="T44" s="66"/>
+      <c r="U44" s="66"/>
+      <c r="V44" s="66"/>
+      <c r="W44" s="66"/>
+      <c r="X44" s="66"/>
+      <c r="Y44" s="66"/>
+      <c r="Z44" s="66"/>
+      <c r="AA44" s="66"/>
+      <c r="AB44" s="66"/>
+      <c r="AC44" s="66"/>
+      <c r="AD44" s="66"/>
+      <c r="AE44" s="67"/>
     </row>
     <row r="45" spans="1:31" ht="17.25" customHeight="1">
       <c r="A45" s="69">
@@ -4089,40 +4060,40 @@
       <c r="AD49" s="68"/>
       <c r="AE49" s="63"/>
     </row>
-    <row r="50" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A50" s="103"/>
-      <c r="B50" s="104"/>
-      <c r="C50" s="104"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="106" t="s">
+    <row r="50" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A50" s="70"/>
+      <c r="B50" s="66"/>
+      <c r="C50" s="66"/>
+      <c r="D50" s="67"/>
+      <c r="E50" s="65" t="s">
         <v>179</v>
       </c>
-      <c r="F50" s="104"/>
-      <c r="G50" s="104"/>
-      <c r="H50" s="104"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="104"/>
-      <c r="K50" s="104"/>
-      <c r="L50" s="104"/>
-      <c r="M50" s="104"/>
-      <c r="N50" s="104"/>
-      <c r="O50" s="104"/>
-      <c r="P50" s="104"/>
-      <c r="Q50" s="104"/>
-      <c r="R50" s="104"/>
-      <c r="S50" s="104"/>
-      <c r="T50" s="104"/>
-      <c r="U50" s="104"/>
-      <c r="V50" s="104"/>
-      <c r="W50" s="104"/>
-      <c r="X50" s="104"/>
-      <c r="Y50" s="104"/>
-      <c r="Z50" s="104"/>
-      <c r="AA50" s="104"/>
-      <c r="AB50" s="104"/>
-      <c r="AC50" s="104"/>
-      <c r="AD50" s="104"/>
-      <c r="AE50" s="105"/>
+      <c r="F50" s="66"/>
+      <c r="G50" s="66"/>
+      <c r="H50" s="66"/>
+      <c r="I50" s="66"/>
+      <c r="J50" s="66"/>
+      <c r="K50" s="66"/>
+      <c r="L50" s="66"/>
+      <c r="M50" s="66"/>
+      <c r="N50" s="66"/>
+      <c r="O50" s="66"/>
+      <c r="P50" s="66"/>
+      <c r="Q50" s="66"/>
+      <c r="R50" s="66"/>
+      <c r="S50" s="66"/>
+      <c r="T50" s="66"/>
+      <c r="U50" s="66"/>
+      <c r="V50" s="66"/>
+      <c r="W50" s="66"/>
+      <c r="X50" s="66"/>
+      <c r="Y50" s="66"/>
+      <c r="Z50" s="66"/>
+      <c r="AA50" s="66"/>
+      <c r="AB50" s="66"/>
+      <c r="AC50" s="66"/>
+      <c r="AD50" s="66"/>
+      <c r="AE50" s="67"/>
     </row>
     <row r="51" spans="1:31" ht="17.25" customHeight="1">
       <c r="A51" s="69">
@@ -5234,792 +5205,797 @@
       <c r="AD86" s="66"/>
       <c r="AE86" s="67"/>
     </row>
-    <row r="87" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A87" s="108">
+    <row r="87" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A87" s="189">
         <v>14</v>
       </c>
-      <c r="B87" s="109"/>
-      <c r="C87" s="109"/>
-      <c r="D87" s="110"/>
-      <c r="E87" s="111" t="s">
+      <c r="B87" s="190"/>
+      <c r="C87" s="190"/>
+      <c r="D87" s="191"/>
+      <c r="E87" s="192" t="s">
         <v>136</v>
       </c>
-      <c r="F87" s="112"/>
-      <c r="G87" s="112"/>
-      <c r="H87" s="112"/>
-      <c r="I87" s="112"/>
-      <c r="J87" s="112"/>
-      <c r="K87" s="112"/>
-      <c r="L87" s="112"/>
-      <c r="M87" s="112"/>
-      <c r="N87" s="112"/>
-      <c r="O87" s="112"/>
-      <c r="P87" s="112"/>
-      <c r="Q87" s="112"/>
-      <c r="R87" s="112"/>
-      <c r="S87" s="112"/>
-      <c r="T87" s="112"/>
-      <c r="U87" s="112"/>
-      <c r="V87" s="112"/>
-      <c r="W87" s="112"/>
-      <c r="X87" s="113"/>
-      <c r="Y87" s="113"/>
-      <c r="Z87" s="113"/>
-      <c r="AA87" s="113"/>
-      <c r="AB87" s="109"/>
-      <c r="AC87" s="109"/>
-      <c r="AD87" s="109"/>
-      <c r="AE87" s="110"/>
-    </row>
-    <row r="88" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A88" s="99"/>
-      <c r="B88" s="100"/>
-      <c r="C88" s="100"/>
-      <c r="D88" s="101"/>
-      <c r="E88" s="114" t="s">
+      <c r="F87" s="193"/>
+      <c r="G87" s="193"/>
+      <c r="H87" s="193"/>
+      <c r="I87" s="193"/>
+      <c r="J87" s="193"/>
+      <c r="K87" s="193"/>
+      <c r="L87" s="193"/>
+      <c r="M87" s="193"/>
+      <c r="N87" s="193"/>
+      <c r="O87" s="193"/>
+      <c r="P87" s="193"/>
+      <c r="Q87" s="193"/>
+      <c r="R87" s="193"/>
+      <c r="S87" s="193"/>
+      <c r="T87" s="193"/>
+      <c r="U87" s="193"/>
+      <c r="V87" s="193"/>
+      <c r="W87" s="193"/>
+      <c r="X87" s="194"/>
+      <c r="Y87" s="194"/>
+      <c r="Z87" s="194"/>
+      <c r="AA87" s="194"/>
+      <c r="AB87" s="190"/>
+      <c r="AC87" s="190"/>
+      <c r="AD87" s="190"/>
+      <c r="AE87" s="191"/>
+    </row>
+    <row r="88" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A88" s="62"/>
+      <c r="B88" s="68"/>
+      <c r="C88" s="68"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="195" t="s">
         <v>140</v>
       </c>
-      <c r="F88" s="115"/>
-      <c r="G88" s="115"/>
-      <c r="H88" s="115"/>
-      <c r="I88" s="115"/>
-      <c r="J88" s="115"/>
-      <c r="K88" s="115"/>
-      <c r="L88" s="115"/>
-      <c r="M88" s="115"/>
-      <c r="N88" s="115"/>
-      <c r="O88" s="115"/>
-      <c r="P88" s="115"/>
-      <c r="Q88" s="115"/>
-      <c r="R88" s="115"/>
-      <c r="S88" s="115"/>
-      <c r="T88" s="115"/>
-      <c r="U88" s="115"/>
-      <c r="V88" s="115"/>
-      <c r="W88" s="115"/>
-      <c r="X88" s="116"/>
-      <c r="Y88" s="116"/>
-      <c r="Z88" s="116"/>
-      <c r="AA88" s="116"/>
-      <c r="AB88" s="100"/>
-      <c r="AC88" s="100"/>
-      <c r="AD88" s="100"/>
-      <c r="AE88" s="101"/>
-    </row>
-    <row r="89" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A89" s="99"/>
-      <c r="B89" s="100"/>
-      <c r="C89" s="100"/>
-      <c r="D89" s="101"/>
-      <c r="E89" s="114" t="s">
+      <c r="F88" s="196"/>
+      <c r="G88" s="196"/>
+      <c r="H88" s="196"/>
+      <c r="I88" s="196"/>
+      <c r="J88" s="196"/>
+      <c r="K88" s="196"/>
+      <c r="L88" s="196"/>
+      <c r="M88" s="196"/>
+      <c r="N88" s="196"/>
+      <c r="O88" s="196"/>
+      <c r="P88" s="196"/>
+      <c r="Q88" s="196"/>
+      <c r="R88" s="196"/>
+      <c r="S88" s="196"/>
+      <c r="T88" s="196"/>
+      <c r="U88" s="196"/>
+      <c r="V88" s="196"/>
+      <c r="W88" s="196"/>
+      <c r="X88" s="197"/>
+      <c r="Y88" s="197"/>
+      <c r="Z88" s="197"/>
+      <c r="AA88" s="197"/>
+      <c r="AB88" s="68"/>
+      <c r="AC88" s="68"/>
+      <c r="AD88" s="68"/>
+      <c r="AE88" s="63"/>
+    </row>
+    <row r="89" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A89" s="62"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="68"/>
+      <c r="D89" s="63"/>
+      <c r="E89" s="195" t="s">
         <v>141</v>
       </c>
-      <c r="F89" s="115"/>
-      <c r="G89" s="115"/>
-      <c r="H89" s="115"/>
-      <c r="I89" s="115"/>
-      <c r="J89" s="115"/>
-      <c r="K89" s="115"/>
-      <c r="L89" s="115"/>
-      <c r="M89" s="115"/>
-      <c r="N89" s="115"/>
-      <c r="O89" s="115"/>
-      <c r="P89" s="115"/>
-      <c r="Q89" s="115"/>
-      <c r="R89" s="115"/>
-      <c r="S89" s="115"/>
-      <c r="T89" s="115"/>
-      <c r="U89" s="115"/>
-      <c r="V89" s="115"/>
-      <c r="W89" s="115"/>
-      <c r="X89" s="116"/>
-      <c r="Y89" s="116"/>
-      <c r="Z89" s="116"/>
-      <c r="AA89" s="116"/>
-      <c r="AB89" s="100"/>
-      <c r="AC89" s="100"/>
-      <c r="AD89" s="100"/>
-      <c r="AE89" s="101"/>
-    </row>
-    <row r="90" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A90" s="99"/>
-      <c r="B90" s="100"/>
-      <c r="C90" s="100"/>
-      <c r="D90" s="101"/>
-      <c r="E90" s="114" t="s">
+      <c r="F89" s="196"/>
+      <c r="G89" s="196"/>
+      <c r="H89" s="196"/>
+      <c r="I89" s="196"/>
+      <c r="J89" s="196"/>
+      <c r="K89" s="196"/>
+      <c r="L89" s="196"/>
+      <c r="M89" s="196"/>
+      <c r="N89" s="196"/>
+      <c r="O89" s="196"/>
+      <c r="P89" s="196"/>
+      <c r="Q89" s="196"/>
+      <c r="R89" s="196"/>
+      <c r="S89" s="196"/>
+      <c r="T89" s="196"/>
+      <c r="U89" s="196"/>
+      <c r="V89" s="196"/>
+      <c r="W89" s="196"/>
+      <c r="X89" s="197"/>
+      <c r="Y89" s="197"/>
+      <c r="Z89" s="197"/>
+      <c r="AA89" s="197"/>
+      <c r="AB89" s="68"/>
+      <c r="AC89" s="68"/>
+      <c r="AD89" s="68"/>
+      <c r="AE89" s="63"/>
+    </row>
+    <row r="90" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A90" s="62"/>
+      <c r="B90" s="68"/>
+      <c r="C90" s="68"/>
+      <c r="D90" s="63"/>
+      <c r="E90" s="195" t="s">
         <v>184</v>
       </c>
-      <c r="F90" s="115"/>
-      <c r="G90" s="115"/>
-      <c r="H90" s="115"/>
-      <c r="I90" s="115"/>
-      <c r="J90" s="115"/>
-      <c r="K90" s="115"/>
-      <c r="L90" s="115"/>
-      <c r="M90" s="115"/>
-      <c r="N90" s="115"/>
-      <c r="O90" s="115"/>
-      <c r="P90" s="115"/>
-      <c r="Q90" s="115"/>
-      <c r="R90" s="115"/>
-      <c r="S90" s="115"/>
-      <c r="T90" s="115"/>
-      <c r="U90" s="115"/>
-      <c r="V90" s="115"/>
-      <c r="W90" s="115"/>
-      <c r="X90" s="116"/>
-      <c r="Y90" s="116"/>
-      <c r="Z90" s="116"/>
-      <c r="AA90" s="116"/>
-      <c r="AB90" s="100"/>
-      <c r="AC90" s="100"/>
-      <c r="AD90" s="100"/>
-      <c r="AE90" s="101"/>
-    </row>
-    <row r="91" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A91" s="99"/>
-      <c r="B91" s="100"/>
-      <c r="C91" s="100"/>
-      <c r="D91" s="101"/>
-      <c r="E91" s="114"/>
-      <c r="F91" s="117" t="s">
+      <c r="F90" s="196"/>
+      <c r="G90" s="196"/>
+      <c r="H90" s="196"/>
+      <c r="I90" s="196"/>
+      <c r="J90" s="196"/>
+      <c r="K90" s="196"/>
+      <c r="L90" s="196"/>
+      <c r="M90" s="196"/>
+      <c r="N90" s="196"/>
+      <c r="O90" s="196"/>
+      <c r="P90" s="196"/>
+      <c r="Q90" s="196"/>
+      <c r="R90" s="196"/>
+      <c r="S90" s="196"/>
+      <c r="T90" s="196"/>
+      <c r="U90" s="196"/>
+      <c r="V90" s="196"/>
+      <c r="W90" s="196"/>
+      <c r="X90" s="197"/>
+      <c r="Y90" s="197"/>
+      <c r="Z90" s="197"/>
+      <c r="AA90" s="197"/>
+      <c r="AB90" s="68"/>
+      <c r="AC90" s="68"/>
+      <c r="AD90" s="68"/>
+      <c r="AE90" s="63"/>
+    </row>
+    <row r="91" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A91" s="62"/>
+      <c r="B91" s="68"/>
+      <c r="C91" s="68"/>
+      <c r="D91" s="63"/>
+      <c r="E91" s="195"/>
+      <c r="F91" s="198" t="s">
         <v>185</v>
       </c>
-      <c r="G91" s="115"/>
-      <c r="H91" s="115"/>
-      <c r="I91" s="115"/>
-      <c r="J91" s="115"/>
-      <c r="K91" s="115"/>
-      <c r="L91" s="115"/>
-      <c r="M91" s="115"/>
-      <c r="N91" s="115"/>
-      <c r="O91" s="115"/>
-      <c r="P91" s="115"/>
-      <c r="Q91" s="115"/>
-      <c r="R91" s="115"/>
-      <c r="S91" s="115"/>
-      <c r="T91" s="115"/>
-      <c r="U91" s="115"/>
-      <c r="V91" s="115"/>
-      <c r="W91" s="115"/>
-      <c r="X91" s="116"/>
-      <c r="Y91" s="116"/>
-      <c r="Z91" s="116"/>
-      <c r="AA91" s="116"/>
-      <c r="AB91" s="100"/>
-      <c r="AC91" s="100"/>
-      <c r="AD91" s="100"/>
-      <c r="AE91" s="101"/>
-    </row>
-    <row r="92" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A92" s="99"/>
-      <c r="B92" s="100"/>
-      <c r="C92" s="100"/>
-      <c r="D92" s="101"/>
-      <c r="E92" s="114"/>
-      <c r="F92" s="117" t="s">
+      <c r="G91" s="196"/>
+      <c r="H91" s="196"/>
+      <c r="I91" s="196"/>
+      <c r="J91" s="196"/>
+      <c r="K91" s="196"/>
+      <c r="L91" s="196"/>
+      <c r="M91" s="196"/>
+      <c r="N91" s="196"/>
+      <c r="O91" s="196"/>
+      <c r="P91" s="196"/>
+      <c r="Q91" s="196"/>
+      <c r="R91" s="196"/>
+      <c r="S91" s="196"/>
+      <c r="T91" s="196"/>
+      <c r="U91" s="196"/>
+      <c r="V91" s="196"/>
+      <c r="W91" s="196"/>
+      <c r="X91" s="197"/>
+      <c r="Y91" s="197"/>
+      <c r="Z91" s="197"/>
+      <c r="AA91" s="197"/>
+      <c r="AB91" s="68"/>
+      <c r="AC91" s="68"/>
+      <c r="AD91" s="68"/>
+      <c r="AE91" s="63"/>
+    </row>
+    <row r="92" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A92" s="62"/>
+      <c r="B92" s="68"/>
+      <c r="C92" s="68"/>
+      <c r="D92" s="63"/>
+      <c r="E92" s="195"/>
+      <c r="F92" s="198" t="s">
         <v>186</v>
       </c>
-      <c r="G92" s="115"/>
-      <c r="H92" s="115"/>
-      <c r="I92" s="115"/>
-      <c r="J92" s="115"/>
-      <c r="K92" s="115"/>
-      <c r="L92" s="115"/>
-      <c r="M92" s="115"/>
-      <c r="N92" s="115"/>
-      <c r="O92" s="115"/>
-      <c r="P92" s="115"/>
-      <c r="Q92" s="115"/>
-      <c r="R92" s="115"/>
-      <c r="S92" s="115"/>
-      <c r="T92" s="115"/>
-      <c r="U92" s="115"/>
-      <c r="V92" s="115"/>
-      <c r="W92" s="115"/>
-      <c r="X92" s="116"/>
-      <c r="Y92" s="116"/>
-      <c r="Z92" s="116"/>
-      <c r="AA92" s="116"/>
-      <c r="AB92" s="100"/>
-      <c r="AC92" s="100"/>
-      <c r="AD92" s="100"/>
-      <c r="AE92" s="101"/>
-    </row>
-    <row r="93" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A93" s="99"/>
-      <c r="B93" s="100"/>
-      <c r="C93" s="100"/>
-      <c r="D93" s="101"/>
-      <c r="E93" s="114" t="s">
+      <c r="G92" s="196"/>
+      <c r="H92" s="196"/>
+      <c r="I92" s="196"/>
+      <c r="J92" s="196"/>
+      <c r="K92" s="196"/>
+      <c r="L92" s="196"/>
+      <c r="M92" s="196"/>
+      <c r="N92" s="196"/>
+      <c r="O92" s="196"/>
+      <c r="P92" s="196"/>
+      <c r="Q92" s="196"/>
+      <c r="R92" s="196"/>
+      <c r="S92" s="196"/>
+      <c r="T92" s="196"/>
+      <c r="U92" s="196"/>
+      <c r="V92" s="196"/>
+      <c r="W92" s="196"/>
+      <c r="X92" s="197"/>
+      <c r="Y92" s="197"/>
+      <c r="Z92" s="197"/>
+      <c r="AA92" s="197"/>
+      <c r="AB92" s="68"/>
+      <c r="AC92" s="68"/>
+      <c r="AD92" s="68"/>
+      <c r="AE92" s="63"/>
+    </row>
+    <row r="93" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A93" s="62"/>
+      <c r="B93" s="68"/>
+      <c r="C93" s="68"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="195" t="s">
         <v>187</v>
       </c>
-      <c r="F93" s="115"/>
-      <c r="G93" s="115"/>
-      <c r="H93" s="115"/>
-      <c r="I93" s="115"/>
-      <c r="J93" s="115"/>
-      <c r="K93" s="115"/>
-      <c r="L93" s="115"/>
-      <c r="M93" s="115"/>
-      <c r="N93" s="115"/>
-      <c r="O93" s="115"/>
-      <c r="P93" s="115"/>
-      <c r="Q93" s="115"/>
-      <c r="R93" s="115"/>
-      <c r="S93" s="115"/>
-      <c r="T93" s="115"/>
-      <c r="U93" s="115"/>
-      <c r="V93" s="115"/>
-      <c r="W93" s="115"/>
-      <c r="X93" s="116"/>
-      <c r="Y93" s="116"/>
-      <c r="Z93" s="116"/>
-      <c r="AA93" s="116"/>
-      <c r="AB93" s="100"/>
-      <c r="AC93" s="100"/>
-      <c r="AD93" s="100"/>
-      <c r="AE93" s="101"/>
-    </row>
-    <row r="94" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A94" s="99"/>
-      <c r="B94" s="100"/>
-      <c r="C94" s="100"/>
-      <c r="D94" s="101"/>
-      <c r="E94" s="114" t="s">
+      <c r="F93" s="196"/>
+      <c r="G93" s="196"/>
+      <c r="H93" s="196"/>
+      <c r="I93" s="196"/>
+      <c r="J93" s="196"/>
+      <c r="K93" s="196"/>
+      <c r="L93" s="196"/>
+      <c r="M93" s="196"/>
+      <c r="N93" s="196"/>
+      <c r="O93" s="196"/>
+      <c r="P93" s="196"/>
+      <c r="Q93" s="196"/>
+      <c r="R93" s="196"/>
+      <c r="S93" s="196"/>
+      <c r="T93" s="196"/>
+      <c r="U93" s="196"/>
+      <c r="V93" s="196"/>
+      <c r="W93" s="196"/>
+      <c r="X93" s="197"/>
+      <c r="Y93" s="197"/>
+      <c r="Z93" s="197"/>
+      <c r="AA93" s="197"/>
+      <c r="AB93" s="68"/>
+      <c r="AC93" s="68"/>
+      <c r="AD93" s="68"/>
+      <c r="AE93" s="63"/>
+    </row>
+    <row r="94" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A94" s="62"/>
+      <c r="B94" s="68"/>
+      <c r="C94" s="68"/>
+      <c r="D94" s="63"/>
+      <c r="E94" s="195" t="s">
         <v>188</v>
       </c>
-      <c r="F94" s="115"/>
-      <c r="G94" s="115"/>
-      <c r="H94" s="115"/>
-      <c r="I94" s="115"/>
-      <c r="J94" s="115"/>
-      <c r="K94" s="115"/>
-      <c r="L94" s="115"/>
-      <c r="M94" s="115"/>
-      <c r="N94" s="115"/>
-      <c r="O94" s="115"/>
-      <c r="P94" s="115"/>
-      <c r="Q94" s="115"/>
-      <c r="R94" s="115"/>
-      <c r="S94" s="115"/>
-      <c r="T94" s="115"/>
-      <c r="U94" s="115"/>
-      <c r="V94" s="115"/>
-      <c r="W94" s="115"/>
-      <c r="X94" s="116"/>
-      <c r="Y94" s="116"/>
-      <c r="Z94" s="116"/>
-      <c r="AA94" s="116"/>
-      <c r="AB94" s="100"/>
-      <c r="AC94" s="100"/>
-      <c r="AD94" s="100"/>
-      <c r="AE94" s="101"/>
-    </row>
-    <row r="95" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A95" s="99"/>
-      <c r="B95" s="100"/>
-      <c r="C95" s="100"/>
-      <c r="D95" s="101"/>
-      <c r="E95" s="114" t="s">
+      <c r="F94" s="196"/>
+      <c r="G94" s="196"/>
+      <c r="H94" s="196"/>
+      <c r="I94" s="196"/>
+      <c r="J94" s="196"/>
+      <c r="K94" s="196"/>
+      <c r="L94" s="196"/>
+      <c r="M94" s="196"/>
+      <c r="N94" s="196"/>
+      <c r="O94" s="196"/>
+      <c r="P94" s="196"/>
+      <c r="Q94" s="196"/>
+      <c r="R94" s="196"/>
+      <c r="S94" s="196"/>
+      <c r="T94" s="196"/>
+      <c r="U94" s="196"/>
+      <c r="V94" s="196"/>
+      <c r="W94" s="196"/>
+      <c r="X94" s="197"/>
+      <c r="Y94" s="197"/>
+      <c r="Z94" s="197"/>
+      <c r="AA94" s="197"/>
+      <c r="AB94" s="68"/>
+      <c r="AC94" s="68"/>
+      <c r="AD94" s="68"/>
+      <c r="AE94" s="63"/>
+    </row>
+    <row r="95" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A95" s="62"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="68"/>
+      <c r="D95" s="63"/>
+      <c r="E95" s="195" t="s">
         <v>189</v>
       </c>
-      <c r="F95" s="115"/>
-      <c r="G95" s="115"/>
-      <c r="H95" s="115"/>
-      <c r="I95" s="115"/>
-      <c r="J95" s="115"/>
-      <c r="K95" s="115"/>
-      <c r="L95" s="115"/>
-      <c r="M95" s="115"/>
-      <c r="N95" s="115"/>
-      <c r="O95" s="115"/>
-      <c r="P95" s="115"/>
-      <c r="Q95" s="115"/>
-      <c r="R95" s="115"/>
-      <c r="S95" s="115"/>
-      <c r="T95" s="115"/>
-      <c r="U95" s="115"/>
-      <c r="V95" s="115"/>
-      <c r="W95" s="115"/>
-      <c r="X95" s="116"/>
-      <c r="Y95" s="116"/>
-      <c r="Z95" s="116"/>
-      <c r="AA95" s="116"/>
-      <c r="AB95" s="100"/>
-      <c r="AC95" s="100"/>
-      <c r="AD95" s="100"/>
-      <c r="AE95" s="101"/>
-    </row>
-    <row r="96" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A96" s="99"/>
-      <c r="B96" s="100"/>
-      <c r="C96" s="100"/>
-      <c r="D96" s="101"/>
-      <c r="E96" s="114" t="s">
+      <c r="F95" s="196"/>
+      <c r="G95" s="196"/>
+      <c r="H95" s="196"/>
+      <c r="I95" s="196"/>
+      <c r="J95" s="196"/>
+      <c r="K95" s="196"/>
+      <c r="L95" s="196"/>
+      <c r="M95" s="196"/>
+      <c r="N95" s="196"/>
+      <c r="O95" s="196"/>
+      <c r="P95" s="196"/>
+      <c r="Q95" s="196"/>
+      <c r="R95" s="196"/>
+      <c r="S95" s="196"/>
+      <c r="T95" s="196"/>
+      <c r="U95" s="196"/>
+      <c r="V95" s="196"/>
+      <c r="W95" s="196"/>
+      <c r="X95" s="197"/>
+      <c r="Y95" s="197"/>
+      <c r="Z95" s="197"/>
+      <c r="AA95" s="197"/>
+      <c r="AB95" s="68"/>
+      <c r="AC95" s="68"/>
+      <c r="AD95" s="68"/>
+      <c r="AE95" s="63"/>
+    </row>
+    <row r="96" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A96" s="62"/>
+      <c r="B96" s="68"/>
+      <c r="C96" s="68"/>
+      <c r="D96" s="63"/>
+      <c r="E96" s="195" t="s">
         <v>194</v>
       </c>
-      <c r="F96" s="115"/>
-      <c r="G96" s="115"/>
-      <c r="H96" s="115"/>
-      <c r="I96" s="115"/>
-      <c r="J96" s="115"/>
-      <c r="K96" s="115"/>
-      <c r="L96" s="115"/>
-      <c r="M96" s="115"/>
-      <c r="N96" s="115"/>
-      <c r="O96" s="115"/>
-      <c r="P96" s="115"/>
-      <c r="Q96" s="115"/>
-      <c r="R96" s="115"/>
-      <c r="S96" s="115"/>
-      <c r="T96" s="115"/>
-      <c r="U96" s="115"/>
-      <c r="V96" s="115"/>
-      <c r="W96" s="115"/>
-      <c r="X96" s="116"/>
-      <c r="Y96" s="116"/>
-      <c r="Z96" s="116"/>
-      <c r="AA96" s="116"/>
-      <c r="AB96" s="100"/>
-      <c r="AC96" s="100"/>
-      <c r="AD96" s="100"/>
-      <c r="AE96" s="101"/>
-    </row>
-    <row r="97" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A97" s="106"/>
-      <c r="B97" s="104"/>
-      <c r="C97" s="104"/>
-      <c r="D97" s="105"/>
-      <c r="E97" s="118" t="s">
+      <c r="F96" s="196"/>
+      <c r="G96" s="196"/>
+      <c r="H96" s="196"/>
+      <c r="I96" s="196"/>
+      <c r="J96" s="196"/>
+      <c r="K96" s="196"/>
+      <c r="L96" s="196"/>
+      <c r="M96" s="196"/>
+      <c r="N96" s="196"/>
+      <c r="O96" s="196"/>
+      <c r="P96" s="196"/>
+      <c r="Q96" s="196"/>
+      <c r="R96" s="196"/>
+      <c r="S96" s="196"/>
+      <c r="T96" s="196"/>
+      <c r="U96" s="196"/>
+      <c r="V96" s="196"/>
+      <c r="W96" s="196"/>
+      <c r="X96" s="197"/>
+      <c r="Y96" s="197"/>
+      <c r="Z96" s="197"/>
+      <c r="AA96" s="197"/>
+      <c r="AB96" s="68"/>
+      <c r="AC96" s="68"/>
+      <c r="AD96" s="68"/>
+      <c r="AE96" s="63"/>
+    </row>
+    <row r="97" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A97" s="65"/>
+      <c r="B97" s="66"/>
+      <c r="C97" s="66"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="199" t="s">
         <v>193</v>
       </c>
-      <c r="F97" s="119"/>
-      <c r="G97" s="119"/>
-      <c r="H97" s="119"/>
-      <c r="I97" s="119"/>
-      <c r="J97" s="119"/>
-      <c r="K97" s="119"/>
-      <c r="L97" s="119"/>
-      <c r="M97" s="119"/>
-      <c r="N97" s="119"/>
-      <c r="O97" s="119"/>
-      <c r="P97" s="119"/>
-      <c r="Q97" s="119"/>
-      <c r="R97" s="119"/>
-      <c r="S97" s="119"/>
-      <c r="T97" s="119"/>
-      <c r="U97" s="119"/>
-      <c r="V97" s="119"/>
-      <c r="W97" s="119"/>
-      <c r="X97" s="120"/>
-      <c r="Y97" s="120"/>
-      <c r="Z97" s="120"/>
-      <c r="AA97" s="120"/>
-      <c r="AB97" s="104"/>
-      <c r="AC97" s="104"/>
-      <c r="AD97" s="104"/>
-      <c r="AE97" s="105"/>
-    </row>
-    <row r="98" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A98" s="123">
+      <c r="F97" s="200"/>
+      <c r="G97" s="200"/>
+      <c r="H97" s="200"/>
+      <c r="I97" s="200"/>
+      <c r="J97" s="200"/>
+      <c r="K97" s="200"/>
+      <c r="L97" s="200"/>
+      <c r="M97" s="200"/>
+      <c r="N97" s="200"/>
+      <c r="O97" s="200"/>
+      <c r="P97" s="200"/>
+      <c r="Q97" s="200"/>
+      <c r="R97" s="200"/>
+      <c r="S97" s="200"/>
+      <c r="T97" s="200"/>
+      <c r="U97" s="200"/>
+      <c r="V97" s="200"/>
+      <c r="W97" s="200"/>
+      <c r="X97" s="201"/>
+      <c r="Y97" s="201"/>
+      <c r="Z97" s="201"/>
+      <c r="AA97" s="201"/>
+      <c r="AB97" s="66"/>
+      <c r="AC97" s="66"/>
+      <c r="AD97" s="66"/>
+      <c r="AE97" s="67"/>
+    </row>
+    <row r="98" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A98" s="202">
         <v>15</v>
       </c>
-      <c r="B98" s="109"/>
-      <c r="C98" s="109"/>
-      <c r="D98" s="110"/>
-      <c r="E98" s="111" t="s">
+      <c r="B98" s="190"/>
+      <c r="C98" s="190"/>
+      <c r="D98" s="191"/>
+      <c r="E98" s="192" t="s">
         <v>136</v>
       </c>
-      <c r="F98" s="109"/>
-      <c r="G98" s="109"/>
-      <c r="H98" s="109"/>
-      <c r="I98" s="109"/>
-      <c r="J98" s="109"/>
-      <c r="K98" s="109"/>
-      <c r="L98" s="109"/>
-      <c r="M98" s="109"/>
-      <c r="N98" s="109"/>
-      <c r="O98" s="109"/>
-      <c r="P98" s="109"/>
-      <c r="Q98" s="109"/>
-      <c r="R98" s="109"/>
-      <c r="S98" s="109"/>
-      <c r="T98" s="109"/>
-      <c r="U98" s="109"/>
-      <c r="V98" s="109"/>
-      <c r="W98" s="109"/>
-      <c r="X98" s="109"/>
-      <c r="Y98" s="109"/>
-      <c r="Z98" s="109"/>
-      <c r="AA98" s="109"/>
-      <c r="AB98" s="109"/>
-      <c r="AC98" s="109"/>
-      <c r="AD98" s="109"/>
-      <c r="AE98" s="110"/>
-    </row>
-    <row r="99" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A99" s="99"/>
-      <c r="B99" s="100"/>
-      <c r="C99" s="100"/>
-      <c r="D99" s="101"/>
-      <c r="E99" s="114" t="s">
+      <c r="F98" s="190"/>
+      <c r="G98" s="190"/>
+      <c r="H98" s="190"/>
+      <c r="I98" s="190"/>
+      <c r="J98" s="190"/>
+      <c r="K98" s="190"/>
+      <c r="L98" s="190"/>
+      <c r="M98" s="190"/>
+      <c r="N98" s="190"/>
+      <c r="O98" s="190"/>
+      <c r="P98" s="190"/>
+      <c r="Q98" s="190"/>
+      <c r="R98" s="190"/>
+      <c r="S98" s="190"/>
+      <c r="T98" s="190"/>
+      <c r="U98" s="190"/>
+      <c r="V98" s="190"/>
+      <c r="W98" s="190"/>
+      <c r="X98" s="190"/>
+      <c r="Y98" s="190"/>
+      <c r="Z98" s="190"/>
+      <c r="AA98" s="190"/>
+      <c r="AB98" s="190"/>
+      <c r="AC98" s="190"/>
+      <c r="AD98" s="190"/>
+      <c r="AE98" s="191"/>
+    </row>
+    <row r="99" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A99" s="62"/>
+      <c r="B99" s="68"/>
+      <c r="C99" s="68"/>
+      <c r="D99" s="63"/>
+      <c r="E99" s="195" t="s">
         <v>140</v>
       </c>
-      <c r="F99" s="100"/>
-      <c r="G99" s="100"/>
-      <c r="H99" s="100"/>
-      <c r="I99" s="100"/>
-      <c r="J99" s="100"/>
-      <c r="K99" s="100"/>
-      <c r="L99" s="100"/>
-      <c r="M99" s="100"/>
-      <c r="N99" s="100"/>
-      <c r="O99" s="100"/>
-      <c r="P99" s="100"/>
-      <c r="Q99" s="100"/>
-      <c r="R99" s="100"/>
-      <c r="S99" s="100"/>
-      <c r="T99" s="100"/>
-      <c r="U99" s="100"/>
-      <c r="V99" s="100"/>
-      <c r="W99" s="100"/>
-      <c r="X99" s="100"/>
-      <c r="Y99" s="100"/>
-      <c r="Z99" s="100"/>
-      <c r="AA99" s="100"/>
-      <c r="AB99" s="100"/>
-      <c r="AC99" s="100"/>
-      <c r="AD99" s="100"/>
-      <c r="AE99" s="101"/>
-    </row>
-    <row r="100" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A100" s="99"/>
-      <c r="B100" s="100"/>
-      <c r="C100" s="100"/>
-      <c r="D100" s="101"/>
-      <c r="E100" s="114" t="s">
+      <c r="F99" s="68"/>
+      <c r="G99" s="68"/>
+      <c r="H99" s="68"/>
+      <c r="I99" s="68"/>
+      <c r="J99" s="68"/>
+      <c r="K99" s="68"/>
+      <c r="L99" s="68"/>
+      <c r="M99" s="68"/>
+      <c r="N99" s="68"/>
+      <c r="O99" s="68"/>
+      <c r="P99" s="68"/>
+      <c r="Q99" s="68"/>
+      <c r="R99" s="68"/>
+      <c r="S99" s="68"/>
+      <c r="T99" s="68"/>
+      <c r="U99" s="68"/>
+      <c r="V99" s="68"/>
+      <c r="W99" s="68"/>
+      <c r="X99" s="68"/>
+      <c r="Y99" s="68"/>
+      <c r="Z99" s="68"/>
+      <c r="AA99" s="68"/>
+      <c r="AB99" s="68"/>
+      <c r="AC99" s="68"/>
+      <c r="AD99" s="68"/>
+      <c r="AE99" s="63"/>
+    </row>
+    <row r="100" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A100" s="62"/>
+      <c r="B100" s="68"/>
+      <c r="C100" s="68"/>
+      <c r="D100" s="63"/>
+      <c r="E100" s="195" t="s">
         <v>141</v>
       </c>
-      <c r="F100" s="100"/>
-      <c r="G100" s="100"/>
-      <c r="H100" s="100"/>
-      <c r="I100" s="100"/>
-      <c r="J100" s="100"/>
-      <c r="K100" s="100"/>
-      <c r="L100" s="100"/>
-      <c r="M100" s="100"/>
-      <c r="N100" s="100"/>
-      <c r="O100" s="100"/>
-      <c r="P100" s="100"/>
-      <c r="Q100" s="100"/>
-      <c r="R100" s="100"/>
-      <c r="S100" s="100"/>
-      <c r="T100" s="100"/>
-      <c r="U100" s="100"/>
-      <c r="V100" s="100"/>
-      <c r="W100" s="100"/>
-      <c r="X100" s="100"/>
-      <c r="Y100" s="100"/>
-      <c r="Z100" s="100"/>
-      <c r="AA100" s="100"/>
-      <c r="AB100" s="100"/>
-      <c r="AC100" s="100"/>
-      <c r="AD100" s="100"/>
-      <c r="AE100" s="101"/>
-    </row>
-    <row r="101" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A101" s="99"/>
-      <c r="B101" s="100"/>
-      <c r="C101" s="100"/>
-      <c r="D101" s="101"/>
-      <c r="E101" s="114"/>
-      <c r="F101" s="100" t="s">
+      <c r="F100" s="68"/>
+      <c r="G100" s="68"/>
+      <c r="H100" s="68"/>
+      <c r="I100" s="68"/>
+      <c r="J100" s="68"/>
+      <c r="K100" s="68"/>
+      <c r="L100" s="68"/>
+      <c r="M100" s="68"/>
+      <c r="N100" s="68"/>
+      <c r="O100" s="68"/>
+      <c r="P100" s="68"/>
+      <c r="Q100" s="68"/>
+      <c r="R100" s="68"/>
+      <c r="S100" s="68"/>
+      <c r="T100" s="68"/>
+      <c r="U100" s="68"/>
+      <c r="V100" s="68"/>
+      <c r="W100" s="68"/>
+      <c r="X100" s="68"/>
+      <c r="Y100" s="68"/>
+      <c r="Z100" s="68"/>
+      <c r="AA100" s="68"/>
+      <c r="AB100" s="68"/>
+      <c r="AC100" s="68"/>
+      <c r="AD100" s="68"/>
+      <c r="AE100" s="63"/>
+    </row>
+    <row r="101" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A101" s="62"/>
+      <c r="B101" s="68"/>
+      <c r="C101" s="68"/>
+      <c r="D101" s="63"/>
+      <c r="E101" s="195"/>
+      <c r="F101" s="68" t="s">
         <v>129</v>
       </c>
-      <c r="G101" s="100"/>
-      <c r="H101" s="100"/>
-      <c r="I101" s="100"/>
-      <c r="J101" s="100"/>
-      <c r="K101" s="100"/>
-      <c r="L101" s="100"/>
-      <c r="M101" s="100"/>
-      <c r="N101" s="100"/>
-      <c r="O101" s="100"/>
-      <c r="P101" s="100"/>
-      <c r="Q101" s="100"/>
-      <c r="R101" s="100"/>
-      <c r="S101" s="100"/>
-      <c r="T101" s="100"/>
-      <c r="U101" s="100"/>
-      <c r="V101" s="100"/>
-      <c r="W101" s="100"/>
-      <c r="X101" s="100"/>
-      <c r="Y101" s="100"/>
-      <c r="Z101" s="100"/>
-      <c r="AA101" s="100"/>
-      <c r="AB101" s="100"/>
-      <c r="AC101" s="100"/>
-      <c r="AD101" s="100"/>
-      <c r="AE101" s="101"/>
-    </row>
-    <row r="102" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A102" s="99"/>
-      <c r="B102" s="100"/>
-      <c r="C102" s="100"/>
-      <c r="D102" s="101"/>
-      <c r="E102" s="114"/>
-      <c r="F102" s="100" t="s">
+      <c r="G101" s="68"/>
+      <c r="H101" s="68"/>
+      <c r="I101" s="68"/>
+      <c r="J101" s="68"/>
+      <c r="K101" s="68"/>
+      <c r="L101" s="68"/>
+      <c r="M101" s="68"/>
+      <c r="N101" s="68"/>
+      <c r="O101" s="68"/>
+      <c r="P101" s="68"/>
+      <c r="Q101" s="68"/>
+      <c r="R101" s="68"/>
+      <c r="S101" s="68"/>
+      <c r="T101" s="68"/>
+      <c r="U101" s="68"/>
+      <c r="V101" s="68"/>
+      <c r="W101" s="68"/>
+      <c r="X101" s="68"/>
+      <c r="Y101" s="68"/>
+      <c r="Z101" s="68"/>
+      <c r="AA101" s="68"/>
+      <c r="AB101" s="68"/>
+      <c r="AC101" s="68"/>
+      <c r="AD101" s="68"/>
+      <c r="AE101" s="63"/>
+    </row>
+    <row r="102" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A102" s="62"/>
+      <c r="B102" s="68"/>
+      <c r="C102" s="68"/>
+      <c r="D102" s="63"/>
+      <c r="E102" s="195"/>
+      <c r="F102" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="G102" s="100"/>
-      <c r="H102" s="100"/>
-      <c r="I102" s="100"/>
-      <c r="J102" s="100"/>
-      <c r="K102" s="100"/>
-      <c r="L102" s="100"/>
-      <c r="M102" s="100"/>
-      <c r="N102" s="100"/>
-      <c r="O102" s="100"/>
-      <c r="P102" s="100"/>
-      <c r="Q102" s="100"/>
-      <c r="R102" s="100"/>
-      <c r="S102" s="100"/>
-      <c r="T102" s="100"/>
-      <c r="U102" s="100"/>
-      <c r="V102" s="100"/>
-      <c r="W102" s="100"/>
-      <c r="X102" s="100"/>
-      <c r="Y102" s="100"/>
-      <c r="Z102" s="100"/>
-      <c r="AA102" s="100"/>
-      <c r="AB102" s="100"/>
-      <c r="AC102" s="100"/>
-      <c r="AD102" s="100"/>
-      <c r="AE102" s="101"/>
-    </row>
-    <row r="103" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A103" s="99"/>
-      <c r="B103" s="100"/>
-      <c r="C103" s="100"/>
-      <c r="D103" s="101"/>
-      <c r="E103" s="114" t="s">
+      <c r="G102" s="68"/>
+      <c r="H102" s="68"/>
+      <c r="I102" s="68"/>
+      <c r="J102" s="68"/>
+      <c r="K102" s="68"/>
+      <c r="L102" s="68"/>
+      <c r="M102" s="68"/>
+      <c r="N102" s="68"/>
+      <c r="O102" s="68"/>
+      <c r="P102" s="68"/>
+      <c r="Q102" s="68"/>
+      <c r="R102" s="68"/>
+      <c r="S102" s="68"/>
+      <c r="T102" s="68"/>
+      <c r="U102" s="68"/>
+      <c r="V102" s="68"/>
+      <c r="W102" s="68"/>
+      <c r="X102" s="68"/>
+      <c r="Y102" s="68"/>
+      <c r="Z102" s="68"/>
+      <c r="AA102" s="68"/>
+      <c r="AB102" s="68"/>
+      <c r="AC102" s="68"/>
+      <c r="AD102" s="68"/>
+      <c r="AE102" s="63"/>
+    </row>
+    <row r="103" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A103" s="62"/>
+      <c r="B103" s="68"/>
+      <c r="C103" s="68"/>
+      <c r="D103" s="63"/>
+      <c r="E103" s="195" t="s">
         <v>184</v>
       </c>
-      <c r="F103" s="115"/>
-      <c r="G103" s="100"/>
-      <c r="H103" s="100"/>
-      <c r="I103" s="100"/>
-      <c r="J103" s="100"/>
-      <c r="K103" s="100"/>
-      <c r="L103" s="100"/>
-      <c r="M103" s="100"/>
-      <c r="N103" s="100"/>
-      <c r="O103" s="100"/>
-      <c r="P103" s="100"/>
-      <c r="Q103" s="100"/>
-      <c r="R103" s="100"/>
-      <c r="S103" s="100"/>
-      <c r="T103" s="100"/>
-      <c r="U103" s="100"/>
-      <c r="V103" s="100"/>
-      <c r="W103" s="100"/>
-      <c r="X103" s="100"/>
-      <c r="Y103" s="100"/>
-      <c r="Z103" s="100"/>
-      <c r="AA103" s="100"/>
-      <c r="AB103" s="100"/>
-      <c r="AC103" s="100"/>
-      <c r="AD103" s="100"/>
-      <c r="AE103" s="101"/>
-    </row>
-    <row r="104" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A104" s="99"/>
-      <c r="B104" s="100"/>
-      <c r="C104" s="100"/>
-      <c r="D104" s="101"/>
-      <c r="E104" s="114"/>
-      <c r="F104" s="117" t="s">
+      <c r="F103" s="196"/>
+      <c r="G103" s="68"/>
+      <c r="H103" s="68"/>
+      <c r="I103" s="68"/>
+      <c r="J103" s="68"/>
+      <c r="K103" s="68"/>
+      <c r="L103" s="68"/>
+      <c r="M103" s="68"/>
+      <c r="N103" s="68"/>
+      <c r="O103" s="68"/>
+      <c r="P103" s="68"/>
+      <c r="Q103" s="68"/>
+      <c r="R103" s="68"/>
+      <c r="S103" s="68"/>
+      <c r="T103" s="68"/>
+      <c r="U103" s="68"/>
+      <c r="V103" s="68"/>
+      <c r="W103" s="68"/>
+      <c r="X103" s="68"/>
+      <c r="Y103" s="68"/>
+      <c r="Z103" s="68"/>
+      <c r="AA103" s="68"/>
+      <c r="AB103" s="68"/>
+      <c r="AC103" s="68"/>
+      <c r="AD103" s="68"/>
+      <c r="AE103" s="63"/>
+    </row>
+    <row r="104" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A104" s="62"/>
+      <c r="B104" s="68"/>
+      <c r="C104" s="68"/>
+      <c r="D104" s="63"/>
+      <c r="E104" s="195"/>
+      <c r="F104" s="198" t="s">
         <v>185</v>
       </c>
-      <c r="G104" s="100"/>
-      <c r="H104" s="100"/>
-      <c r="I104" s="100"/>
-      <c r="J104" s="100"/>
-      <c r="K104" s="100"/>
-      <c r="L104" s="100"/>
-      <c r="M104" s="100"/>
-      <c r="N104" s="100"/>
-      <c r="O104" s="100"/>
-      <c r="P104" s="100"/>
-      <c r="Q104" s="100"/>
-      <c r="R104" s="100"/>
-      <c r="S104" s="100"/>
-      <c r="T104" s="100"/>
-      <c r="U104" s="100"/>
-      <c r="V104" s="100"/>
-      <c r="W104" s="100"/>
-      <c r="X104" s="100"/>
-      <c r="Y104" s="100"/>
-      <c r="Z104" s="100"/>
-      <c r="AA104" s="100"/>
-      <c r="AB104" s="100"/>
-      <c r="AC104" s="100"/>
-      <c r="AD104" s="100"/>
-      <c r="AE104" s="101"/>
-    </row>
-    <row r="105" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A105" s="99"/>
-      <c r="B105" s="100"/>
-      <c r="C105" s="100"/>
-      <c r="D105" s="101"/>
-      <c r="E105" s="114"/>
-      <c r="F105" s="117" t="s">
+      <c r="G104" s="68"/>
+      <c r="H104" s="68"/>
+      <c r="I104" s="68"/>
+      <c r="J104" s="68"/>
+      <c r="K104" s="68"/>
+      <c r="L104" s="68"/>
+      <c r="M104" s="68"/>
+      <c r="N104" s="68"/>
+      <c r="O104" s="68"/>
+      <c r="P104" s="68"/>
+      <c r="Q104" s="68"/>
+      <c r="R104" s="68"/>
+      <c r="S104" s="68"/>
+      <c r="T104" s="68"/>
+      <c r="U104" s="68"/>
+      <c r="V104" s="68"/>
+      <c r="W104" s="68"/>
+      <c r="X104" s="68"/>
+      <c r="Y104" s="68"/>
+      <c r="Z104" s="68"/>
+      <c r="AA104" s="68"/>
+      <c r="AB104" s="68"/>
+      <c r="AC104" s="68"/>
+      <c r="AD104" s="68"/>
+      <c r="AE104" s="63"/>
+    </row>
+    <row r="105" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A105" s="62"/>
+      <c r="B105" s="68"/>
+      <c r="C105" s="68"/>
+      <c r="D105" s="63"/>
+      <c r="E105" s="195"/>
+      <c r="F105" s="198" t="s">
         <v>195</v>
       </c>
-      <c r="G105" s="100"/>
-      <c r="H105" s="100"/>
-      <c r="I105" s="100"/>
-      <c r="J105" s="100"/>
-      <c r="K105" s="100"/>
-      <c r="L105" s="100"/>
-      <c r="M105" s="100"/>
-      <c r="N105" s="100"/>
-      <c r="O105" s="100"/>
-      <c r="P105" s="100"/>
-      <c r="Q105" s="100"/>
-      <c r="R105" s="100"/>
-      <c r="S105" s="100"/>
-      <c r="T105" s="100"/>
-      <c r="U105" s="100"/>
-      <c r="V105" s="100"/>
-      <c r="W105" s="100"/>
-      <c r="X105" s="100"/>
-      <c r="Y105" s="100"/>
-      <c r="Z105" s="100"/>
-      <c r="AA105" s="100"/>
-      <c r="AB105" s="100"/>
-      <c r="AC105" s="100"/>
-      <c r="AD105" s="100"/>
-      <c r="AE105" s="101"/>
-    </row>
-    <row r="106" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A106" s="99"/>
-      <c r="B106" s="100"/>
-      <c r="C106" s="100"/>
-      <c r="D106" s="101"/>
-      <c r="E106" s="114" t="s">
+      <c r="G105" s="68"/>
+      <c r="H105" s="68"/>
+      <c r="I105" s="68"/>
+      <c r="J105" s="68"/>
+      <c r="K105" s="68"/>
+      <c r="L105" s="68"/>
+      <c r="M105" s="68"/>
+      <c r="N105" s="68"/>
+      <c r="O105" s="68"/>
+      <c r="P105" s="68"/>
+      <c r="Q105" s="68"/>
+      <c r="R105" s="68"/>
+      <c r="S105" s="68"/>
+      <c r="T105" s="68"/>
+      <c r="U105" s="68"/>
+      <c r="V105" s="68"/>
+      <c r="W105" s="68"/>
+      <c r="X105" s="68"/>
+      <c r="Y105" s="68"/>
+      <c r="Z105" s="68"/>
+      <c r="AA105" s="68"/>
+      <c r="AB105" s="68"/>
+      <c r="AC105" s="68"/>
+      <c r="AD105" s="68"/>
+      <c r="AE105" s="63"/>
+    </row>
+    <row r="106" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A106" s="62"/>
+      <c r="B106" s="68"/>
+      <c r="C106" s="68"/>
+      <c r="D106" s="63"/>
+      <c r="E106" s="195" t="s">
         <v>187</v>
       </c>
-      <c r="F106" s="100"/>
-      <c r="G106" s="100"/>
-      <c r="H106" s="100"/>
-      <c r="I106" s="100"/>
-      <c r="J106" s="100"/>
-      <c r="K106" s="100"/>
-      <c r="L106" s="100"/>
-      <c r="M106" s="100"/>
-      <c r="N106" s="100"/>
-      <c r="O106" s="100"/>
-      <c r="P106" s="100"/>
-      <c r="Q106" s="100"/>
-      <c r="R106" s="100"/>
-      <c r="S106" s="100"/>
-      <c r="T106" s="100"/>
-      <c r="U106" s="100"/>
-      <c r="V106" s="100"/>
-      <c r="W106" s="100"/>
-      <c r="X106" s="100"/>
-      <c r="Y106" s="100"/>
-      <c r="Z106" s="100"/>
-      <c r="AA106" s="100"/>
-      <c r="AB106" s="100"/>
-      <c r="AC106" s="100"/>
-      <c r="AD106" s="100"/>
-      <c r="AE106" s="101"/>
-    </row>
-    <row r="107" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A107" s="99"/>
-      <c r="B107" s="100"/>
-      <c r="C107" s="100"/>
-      <c r="D107" s="101"/>
-      <c r="E107" s="114" t="s">
+      <c r="F106" s="68"/>
+      <c r="G106" s="68"/>
+      <c r="H106" s="68"/>
+      <c r="I106" s="68"/>
+      <c r="J106" s="68"/>
+      <c r="K106" s="68"/>
+      <c r="L106" s="68"/>
+      <c r="M106" s="68"/>
+      <c r="N106" s="68"/>
+      <c r="O106" s="68"/>
+      <c r="P106" s="68"/>
+      <c r="Q106" s="68"/>
+      <c r="R106" s="68"/>
+      <c r="S106" s="68"/>
+      <c r="T106" s="68"/>
+      <c r="U106" s="68"/>
+      <c r="V106" s="68"/>
+      <c r="W106" s="68"/>
+      <c r="X106" s="68"/>
+      <c r="Y106" s="68"/>
+      <c r="Z106" s="68"/>
+      <c r="AA106" s="68"/>
+      <c r="AB106" s="68"/>
+      <c r="AC106" s="68"/>
+      <c r="AD106" s="68"/>
+      <c r="AE106" s="63"/>
+    </row>
+    <row r="107" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A107" s="62"/>
+      <c r="B107" s="68"/>
+      <c r="C107" s="68"/>
+      <c r="D107" s="63"/>
+      <c r="E107" s="195" t="s">
         <v>188</v>
       </c>
-      <c r="F107" s="100"/>
-      <c r="G107" s="100"/>
-      <c r="H107" s="100"/>
-      <c r="I107" s="100"/>
-      <c r="J107" s="100"/>
-      <c r="K107" s="100"/>
-      <c r="L107" s="100"/>
-      <c r="M107" s="100"/>
-      <c r="N107" s="100"/>
-      <c r="O107" s="100"/>
-      <c r="P107" s="100"/>
-      <c r="Q107" s="100"/>
-      <c r="R107" s="100"/>
-      <c r="S107" s="100"/>
-      <c r="T107" s="100"/>
-      <c r="U107" s="100"/>
-      <c r="V107" s="100"/>
-      <c r="W107" s="100"/>
-      <c r="X107" s="100"/>
-      <c r="Y107" s="100"/>
-      <c r="Z107" s="100"/>
-      <c r="AA107" s="100"/>
-      <c r="AB107" s="100"/>
-      <c r="AC107" s="100"/>
-      <c r="AD107" s="100"/>
-      <c r="AE107" s="101"/>
-    </row>
-    <row r="108" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="D108" s="101"/>
-      <c r="E108" s="121" t="s">
+      <c r="F107" s="68"/>
+      <c r="G107" s="68"/>
+      <c r="H107" s="68"/>
+      <c r="I107" s="68"/>
+      <c r="J107" s="68"/>
+      <c r="K107" s="68"/>
+      <c r="L107" s="68"/>
+      <c r="M107" s="68"/>
+      <c r="N107" s="68"/>
+      <c r="O107" s="68"/>
+      <c r="P107" s="68"/>
+      <c r="Q107" s="68"/>
+      <c r="R107" s="68"/>
+      <c r="S107" s="68"/>
+      <c r="T107" s="68"/>
+      <c r="U107" s="68"/>
+      <c r="V107" s="68"/>
+      <c r="W107" s="68"/>
+      <c r="X107" s="68"/>
+      <c r="Y107" s="68"/>
+      <c r="Z107" s="68"/>
+      <c r="AA107" s="68"/>
+      <c r="AB107" s="68"/>
+      <c r="AC107" s="68"/>
+      <c r="AD107" s="68"/>
+      <c r="AE107" s="63"/>
+    </row>
+    <row r="108" spans="1:31" ht="17.25" customHeight="1">
+      <c r="D108" s="63"/>
+      <c r="E108" s="99" t="s">
         <v>196</v>
       </c>
-      <c r="AE108" s="101"/>
-    </row>
-    <row r="109" spans="1:31" s="102" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A109" s="104"/>
-      <c r="B109" s="104"/>
-      <c r="C109" s="104"/>
-      <c r="D109" s="105"/>
-      <c r="E109" s="122" t="s">
+      <c r="AE108" s="63"/>
+    </row>
+    <row r="109" spans="1:31" ht="17.25" customHeight="1">
+      <c r="A109" s="66"/>
+      <c r="B109" s="66"/>
+      <c r="C109" s="66"/>
+      <c r="D109" s="67"/>
+      <c r="E109" s="203" t="s">
         <v>197</v>
       </c>
-      <c r="F109" s="104"/>
-      <c r="G109" s="104"/>
-      <c r="H109" s="104"/>
-      <c r="I109" s="104"/>
-      <c r="J109" s="104"/>
-      <c r="K109" s="104"/>
-      <c r="L109" s="104"/>
-      <c r="M109" s="104"/>
-      <c r="N109" s="104"/>
-      <c r="O109" s="104"/>
-      <c r="P109" s="104"/>
-      <c r="Q109" s="104"/>
-      <c r="R109" s="104"/>
-      <c r="S109" s="104"/>
-      <c r="T109" s="104"/>
-      <c r="U109" s="104"/>
-      <c r="V109" s="104"/>
-      <c r="W109" s="104"/>
-      <c r="X109" s="104"/>
-      <c r="Y109" s="104"/>
-      <c r="Z109" s="104"/>
-      <c r="AA109" s="104"/>
-      <c r="AB109" s="104"/>
-      <c r="AC109" s="104"/>
-      <c r="AD109" s="104"/>
-      <c r="AE109" s="105"/>
+      <c r="F109" s="66"/>
+      <c r="G109" s="66"/>
+      <c r="H109" s="66"/>
+      <c r="I109" s="66"/>
+      <c r="J109" s="66"/>
+      <c r="K109" s="66"/>
+      <c r="L109" s="66"/>
+      <c r="M109" s="66"/>
+      <c r="N109" s="66"/>
+      <c r="O109" s="66"/>
+      <c r="P109" s="66"/>
+      <c r="Q109" s="66"/>
+      <c r="R109" s="66"/>
+      <c r="S109" s="66"/>
+      <c r="T109" s="66"/>
+      <c r="U109" s="66"/>
+      <c r="V109" s="66"/>
+      <c r="W109" s="66"/>
+      <c r="X109" s="66"/>
+      <c r="Y109" s="66"/>
+      <c r="Z109" s="66"/>
+      <c r="AA109" s="66"/>
+      <c r="AB109" s="66"/>
+      <c r="AC109" s="66"/>
+      <c r="AD109" s="66"/>
+      <c r="AE109" s="67"/>
     </row>
     <row r="110" spans="1:31" ht="17.25" customHeight="1">
-      <c r="E110" s="107"/>
+      <c r="E110" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A5:D6"/>
+    <mergeCell ref="E5:AE6"/>
+    <mergeCell ref="T1:Z1"/>
+    <mergeCell ref="AA1:AJ1"/>
+    <mergeCell ref="A1:S2"/>
     <mergeCell ref="AW1:AZ2"/>
     <mergeCell ref="T2:Z2"/>
     <mergeCell ref="AA2:AJ2"/>
@@ -6028,11 +6004,6 @@
     <mergeCell ref="AU1:AV2"/>
     <mergeCell ref="AO1:AT1"/>
     <mergeCell ref="AO2:AT2"/>
-    <mergeCell ref="A5:D6"/>
-    <mergeCell ref="E5:AE6"/>
-    <mergeCell ref="T1:Z1"/>
-    <mergeCell ref="AA1:AJ1"/>
-    <mergeCell ref="A1:S2"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6049,146 +6020,146 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:78" s="61" customFormat="1" ht="18.75" customHeight="1" thickTop="1">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
-      <c r="U1" s="135"/>
-      <c r="V1" s="172" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="W1" s="172"/>
-      <c r="X1" s="172"/>
-      <c r="Y1" s="172"/>
-      <c r="Z1" s="172"/>
-      <c r="AA1" s="172"/>
-      <c r="AB1" s="172"/>
-      <c r="AC1" s="172"/>
-      <c r="AD1" s="172"/>
-      <c r="AE1" s="140"/>
-      <c r="AF1" s="140"/>
-      <c r="AG1" s="140"/>
-      <c r="AH1" s="140"/>
-      <c r="AI1" s="140"/>
-      <c r="AJ1" s="140"/>
-      <c r="AK1" s="140"/>
-      <c r="AL1" s="140"/>
-      <c r="AM1" s="140"/>
-      <c r="AN1" s="140"/>
-      <c r="AO1" s="172" t="s">
+      <c r="W1" s="146"/>
+      <c r="X1" s="146"/>
+      <c r="Y1" s="146"/>
+      <c r="Z1" s="146"/>
+      <c r="AA1" s="146"/>
+      <c r="AB1" s="146"/>
+      <c r="AC1" s="146"/>
+      <c r="AD1" s="146"/>
+      <c r="AE1" s="114"/>
+      <c r="AF1" s="114"/>
+      <c r="AG1" s="114"/>
+      <c r="AH1" s="114"/>
+      <c r="AI1" s="114"/>
+      <c r="AJ1" s="114"/>
+      <c r="AK1" s="114"/>
+      <c r="AL1" s="114"/>
+      <c r="AM1" s="114"/>
+      <c r="AN1" s="114"/>
+      <c r="AO1" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="AP1" s="172"/>
-      <c r="AQ1" s="172"/>
-      <c r="AR1" s="172"/>
-      <c r="AS1" s="149">
+      <c r="AP1" s="146"/>
+      <c r="AQ1" s="146"/>
+      <c r="AR1" s="146"/>
+      <c r="AS1" s="147">
         <v>45583</v>
       </c>
-      <c r="AT1" s="149"/>
-      <c r="AU1" s="149"/>
-      <c r="AV1" s="149"/>
-      <c r="AW1" s="149"/>
-      <c r="AX1" s="149"/>
-      <c r="AY1" s="149"/>
-      <c r="AZ1" s="149"/>
-      <c r="BA1" s="149"/>
-      <c r="BB1" s="149"/>
-      <c r="BC1" s="173" t="s">
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="147"/>
+      <c r="AV1" s="147"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="147"/>
+      <c r="BA1" s="147"/>
+      <c r="BB1" s="147"/>
+      <c r="BC1" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="BD1" s="174"/>
-      <c r="BE1" s="141"/>
-      <c r="BF1" s="142"/>
-      <c r="BG1" s="142"/>
-      <c r="BH1" s="143"/>
+      <c r="BD1" s="149"/>
+      <c r="BE1" s="101"/>
+      <c r="BF1" s="102"/>
+      <c r="BG1" s="102"/>
+      <c r="BH1" s="103"/>
     </row>
     <row r="2" spans="1:78" s="61" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="136"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="137"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="194" t="s">
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
+      <c r="P2" s="119"/>
+      <c r="Q2" s="119"/>
+      <c r="R2" s="119"/>
+      <c r="S2" s="119"/>
+      <c r="T2" s="119"/>
+      <c r="U2" s="120"/>
+      <c r="V2" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="194"/>
-      <c r="X2" s="194"/>
-      <c r="Y2" s="194"/>
-      <c r="Z2" s="194"/>
-      <c r="AA2" s="194"/>
-      <c r="AB2" s="194"/>
-      <c r="AC2" s="194"/>
-      <c r="AD2" s="194"/>
-      <c r="AE2" s="148" t="s">
+      <c r="W2" s="145"/>
+      <c r="X2" s="145"/>
+      <c r="Y2" s="145"/>
+      <c r="Z2" s="145"/>
+      <c r="AA2" s="145"/>
+      <c r="AB2" s="145"/>
+      <c r="AC2" s="145"/>
+      <c r="AD2" s="145"/>
+      <c r="AE2" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="AF2" s="148"/>
-      <c r="AG2" s="148"/>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="148"/>
-      <c r="AJ2" s="148"/>
-      <c r="AK2" s="148"/>
-      <c r="AL2" s="148"/>
-      <c r="AM2" s="148"/>
-      <c r="AN2" s="148"/>
-      <c r="AO2" s="194" t="s">
+      <c r="AF2" s="107"/>
+      <c r="AG2" s="107"/>
+      <c r="AH2" s="107"/>
+      <c r="AI2" s="107"/>
+      <c r="AJ2" s="107"/>
+      <c r="AK2" s="107"/>
+      <c r="AL2" s="107"/>
+      <c r="AM2" s="107"/>
+      <c r="AN2" s="107"/>
+      <c r="AO2" s="145" t="s">
         <v>5</v>
       </c>
-      <c r="AP2" s="194"/>
-      <c r="AQ2" s="194"/>
-      <c r="AR2" s="194"/>
-      <c r="AS2" s="148" t="s">
+      <c r="AP2" s="145"/>
+      <c r="AQ2" s="145"/>
+      <c r="AR2" s="145"/>
+      <c r="AS2" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="AT2" s="148"/>
-      <c r="AU2" s="148"/>
-      <c r="AV2" s="148"/>
-      <c r="AW2" s="148"/>
-      <c r="AX2" s="148"/>
-      <c r="AY2" s="148"/>
-      <c r="AZ2" s="148"/>
-      <c r="BA2" s="148"/>
-      <c r="BB2" s="148"/>
-      <c r="BC2" s="175"/>
-      <c r="BD2" s="176"/>
-      <c r="BE2" s="144"/>
-      <c r="BF2" s="145"/>
-      <c r="BG2" s="145"/>
-      <c r="BH2" s="146"/>
+      <c r="AT2" s="107"/>
+      <c r="AU2" s="107"/>
+      <c r="AV2" s="107"/>
+      <c r="AW2" s="107"/>
+      <c r="AX2" s="107"/>
+      <c r="AY2" s="107"/>
+      <c r="AZ2" s="107"/>
+      <c r="BA2" s="107"/>
+      <c r="BB2" s="107"/>
+      <c r="BC2" s="150"/>
+      <c r="BD2" s="151"/>
+      <c r="BE2" s="104"/>
+      <c r="BF2" s="105"/>
+      <c r="BG2" s="105"/>
+      <c r="BH2" s="106"/>
     </row>
     <row r="3" spans="1:78" ht="18.75" customHeight="1" thickTop="1"/>
     <row r="4" spans="1:78" ht="18.75" customHeight="1">
@@ -6257,190 +6228,190 @@
       <c r="BK4" s="71"/>
     </row>
     <row r="5" spans="1:78" s="3" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A5" s="177" t="s">
+      <c r="A5" s="152" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="177"/>
-      <c r="C5" s="177" t="s">
+      <c r="B5" s="152"/>
+      <c r="C5" s="152" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="177"/>
-      <c r="E5" s="177"/>
-      <c r="F5" s="177"/>
-      <c r="G5" s="177"/>
-      <c r="H5" s="177"/>
-      <c r="I5" s="177"/>
-      <c r="J5" s="179" t="s">
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="152"/>
+      <c r="J5" s="154" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="180"/>
-      <c r="Q5" s="180"/>
-      <c r="R5" s="180"/>
-      <c r="S5" s="180"/>
-      <c r="T5" s="180"/>
-      <c r="U5" s="180"/>
-      <c r="V5" s="180"/>
-      <c r="W5" s="180"/>
-      <c r="X5" s="181"/>
-      <c r="Y5" s="182" t="s">
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="155"/>
+      <c r="Q5" s="155"/>
+      <c r="R5" s="155"/>
+      <c r="S5" s="155"/>
+      <c r="T5" s="155"/>
+      <c r="U5" s="155"/>
+      <c r="V5" s="155"/>
+      <c r="W5" s="155"/>
+      <c r="X5" s="156"/>
+      <c r="Y5" s="157" t="s">
         <v>10</v>
       </c>
-      <c r="Z5" s="182"/>
-      <c r="AA5" s="182"/>
-      <c r="AB5" s="182"/>
-      <c r="AC5" s="182"/>
-      <c r="AD5" s="182"/>
-      <c r="AE5" s="183"/>
-      <c r="AF5" s="186" t="s">
+      <c r="Z5" s="157"/>
+      <c r="AA5" s="157"/>
+      <c r="AB5" s="157"/>
+      <c r="AC5" s="157"/>
+      <c r="AD5" s="157"/>
+      <c r="AE5" s="158"/>
+      <c r="AF5" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="AG5" s="182"/>
-      <c r="AH5" s="182"/>
-      <c r="AI5" s="182"/>
-      <c r="AJ5" s="182"/>
-      <c r="AK5" s="182"/>
-      <c r="AL5" s="182"/>
-      <c r="AM5" s="182"/>
-      <c r="AN5" s="182"/>
-      <c r="AO5" s="182"/>
-      <c r="AP5" s="182"/>
-      <c r="AQ5" s="182"/>
-      <c r="AR5" s="182"/>
-      <c r="AS5" s="183"/>
-      <c r="AT5" s="188" t="s">
+      <c r="AG5" s="157"/>
+      <c r="AH5" s="157"/>
+      <c r="AI5" s="157"/>
+      <c r="AJ5" s="157"/>
+      <c r="AK5" s="157"/>
+      <c r="AL5" s="157"/>
+      <c r="AM5" s="157"/>
+      <c r="AN5" s="157"/>
+      <c r="AO5" s="157"/>
+      <c r="AP5" s="157"/>
+      <c r="AQ5" s="157"/>
+      <c r="AR5" s="157"/>
+      <c r="AS5" s="158"/>
+      <c r="AT5" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="AU5" s="189"/>
-      <c r="AV5" s="189"/>
-      <c r="AW5" s="189"/>
-      <c r="AX5" s="189"/>
-      <c r="AY5" s="189"/>
-      <c r="AZ5" s="189"/>
-      <c r="BA5" s="189"/>
-      <c r="BB5" s="189"/>
-      <c r="BC5" s="189"/>
-      <c r="BD5" s="189"/>
-      <c r="BE5" s="190"/>
-      <c r="BF5" s="188" t="s">
+      <c r="AU5" s="140"/>
+      <c r="AV5" s="140"/>
+      <c r="AW5" s="140"/>
+      <c r="AX5" s="140"/>
+      <c r="AY5" s="140"/>
+      <c r="AZ5" s="140"/>
+      <c r="BA5" s="140"/>
+      <c r="BB5" s="140"/>
+      <c r="BC5" s="140"/>
+      <c r="BD5" s="140"/>
+      <c r="BE5" s="141"/>
+      <c r="BF5" s="139" t="s">
         <v>13</v>
       </c>
-      <c r="BG5" s="189"/>
-      <c r="BH5" s="189"/>
-      <c r="BI5" s="189"/>
-      <c r="BJ5" s="189"/>
-      <c r="BK5" s="189"/>
-      <c r="BL5" s="189"/>
-      <c r="BM5" s="189"/>
-      <c r="BN5" s="189"/>
-      <c r="BO5" s="189"/>
-      <c r="BP5" s="188" t="s">
+      <c r="BG5" s="140"/>
+      <c r="BH5" s="140"/>
+      <c r="BI5" s="140"/>
+      <c r="BJ5" s="140"/>
+      <c r="BK5" s="140"/>
+      <c r="BL5" s="140"/>
+      <c r="BM5" s="140"/>
+      <c r="BN5" s="140"/>
+      <c r="BO5" s="140"/>
+      <c r="BP5" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="BQ5" s="189"/>
-      <c r="BR5" s="190"/>
-      <c r="BS5" s="188" t="s">
+      <c r="BQ5" s="140"/>
+      <c r="BR5" s="141"/>
+      <c r="BS5" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="BT5" s="189"/>
-      <c r="BU5" s="189"/>
-      <c r="BV5" s="190"/>
-      <c r="BW5" s="188" t="s">
+      <c r="BT5" s="140"/>
+      <c r="BU5" s="140"/>
+      <c r="BV5" s="141"/>
+      <c r="BW5" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="BX5" s="189"/>
-      <c r="BY5" s="189"/>
-      <c r="BZ5" s="190"/>
+      <c r="BX5" s="140"/>
+      <c r="BY5" s="140"/>
+      <c r="BZ5" s="141"/>
     </row>
     <row r="6" spans="1:78" s="3" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A6" s="178"/>
-      <c r="B6" s="178"/>
-      <c r="C6" s="178"/>
-      <c r="D6" s="178"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="178"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="178"/>
-      <c r="J6" s="177" t="s">
+      <c r="A6" s="153"/>
+      <c r="B6" s="153"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="153"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="153"/>
+      <c r="G6" s="153"/>
+      <c r="H6" s="153"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="177"/>
-      <c r="L6" s="177"/>
-      <c r="M6" s="177"/>
-      <c r="N6" s="177"/>
-      <c r="O6" s="179" t="s">
+      <c r="K6" s="152"/>
+      <c r="L6" s="152"/>
+      <c r="M6" s="152"/>
+      <c r="N6" s="152"/>
+      <c r="O6" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="P6" s="180"/>
-      <c r="Q6" s="180"/>
-      <c r="R6" s="180"/>
-      <c r="S6" s="180"/>
-      <c r="T6" s="180"/>
-      <c r="U6" s="179" t="s">
+      <c r="P6" s="155"/>
+      <c r="Q6" s="155"/>
+      <c r="R6" s="155"/>
+      <c r="S6" s="155"/>
+      <c r="T6" s="155"/>
+      <c r="U6" s="154" t="s">
         <v>19</v>
       </c>
-      <c r="V6" s="180"/>
-      <c r="W6" s="180"/>
-      <c r="X6" s="181"/>
-      <c r="Y6" s="184"/>
-      <c r="Z6" s="184"/>
-      <c r="AA6" s="184"/>
-      <c r="AB6" s="184"/>
-      <c r="AC6" s="184"/>
-      <c r="AD6" s="184"/>
-      <c r="AE6" s="185"/>
-      <c r="AF6" s="187"/>
-      <c r="AG6" s="184"/>
-      <c r="AH6" s="184"/>
-      <c r="AI6" s="184"/>
-      <c r="AJ6" s="184"/>
-      <c r="AK6" s="184"/>
-      <c r="AL6" s="184"/>
-      <c r="AM6" s="184"/>
-      <c r="AN6" s="184"/>
-      <c r="AO6" s="184"/>
-      <c r="AP6" s="184"/>
-      <c r="AQ6" s="184"/>
-      <c r="AR6" s="184"/>
-      <c r="AS6" s="185"/>
-      <c r="AT6" s="191"/>
-      <c r="AU6" s="192"/>
-      <c r="AV6" s="192"/>
-      <c r="AW6" s="192"/>
-      <c r="AX6" s="192"/>
-      <c r="AY6" s="192"/>
-      <c r="AZ6" s="192"/>
-      <c r="BA6" s="192"/>
-      <c r="BB6" s="192"/>
-      <c r="BC6" s="192"/>
-      <c r="BD6" s="192"/>
-      <c r="BE6" s="193"/>
-      <c r="BF6" s="191"/>
-      <c r="BG6" s="192"/>
-      <c r="BH6" s="192"/>
-      <c r="BI6" s="192"/>
-      <c r="BJ6" s="192"/>
-      <c r="BK6" s="192"/>
-      <c r="BL6" s="192"/>
-      <c r="BM6" s="192"/>
-      <c r="BN6" s="192"/>
-      <c r="BO6" s="192"/>
-      <c r="BP6" s="191"/>
-      <c r="BQ6" s="192"/>
-      <c r="BR6" s="193"/>
-      <c r="BS6" s="191"/>
-      <c r="BT6" s="192"/>
-      <c r="BU6" s="192"/>
-      <c r="BV6" s="193"/>
-      <c r="BW6" s="191"/>
-      <c r="BX6" s="192"/>
-      <c r="BY6" s="192"/>
-      <c r="BZ6" s="193"/>
+      <c r="V6" s="155"/>
+      <c r="W6" s="155"/>
+      <c r="X6" s="156"/>
+      <c r="Y6" s="159"/>
+      <c r="Z6" s="159"/>
+      <c r="AA6" s="159"/>
+      <c r="AB6" s="159"/>
+      <c r="AC6" s="159"/>
+      <c r="AD6" s="159"/>
+      <c r="AE6" s="160"/>
+      <c r="AF6" s="162"/>
+      <c r="AG6" s="159"/>
+      <c r="AH6" s="159"/>
+      <c r="AI6" s="159"/>
+      <c r="AJ6" s="159"/>
+      <c r="AK6" s="159"/>
+      <c r="AL6" s="159"/>
+      <c r="AM6" s="159"/>
+      <c r="AN6" s="159"/>
+      <c r="AO6" s="159"/>
+      <c r="AP6" s="159"/>
+      <c r="AQ6" s="159"/>
+      <c r="AR6" s="159"/>
+      <c r="AS6" s="160"/>
+      <c r="AT6" s="142"/>
+      <c r="AU6" s="143"/>
+      <c r="AV6" s="143"/>
+      <c r="AW6" s="143"/>
+      <c r="AX6" s="143"/>
+      <c r="AY6" s="143"/>
+      <c r="AZ6" s="143"/>
+      <c r="BA6" s="143"/>
+      <c r="BB6" s="143"/>
+      <c r="BC6" s="143"/>
+      <c r="BD6" s="143"/>
+      <c r="BE6" s="144"/>
+      <c r="BF6" s="142"/>
+      <c r="BG6" s="143"/>
+      <c r="BH6" s="143"/>
+      <c r="BI6" s="143"/>
+      <c r="BJ6" s="143"/>
+      <c r="BK6" s="143"/>
+      <c r="BL6" s="143"/>
+      <c r="BM6" s="143"/>
+      <c r="BN6" s="143"/>
+      <c r="BO6" s="143"/>
+      <c r="BP6" s="142"/>
+      <c r="BQ6" s="143"/>
+      <c r="BR6" s="144"/>
+      <c r="BS6" s="142"/>
+      <c r="BT6" s="143"/>
+      <c r="BU6" s="143"/>
+      <c r="BV6" s="144"/>
+      <c r="BW6" s="142"/>
+      <c r="BX6" s="143"/>
+      <c r="BY6" s="143"/>
+      <c r="BZ6" s="144"/>
     </row>
     <row r="7" spans="1:78" ht="18.75" customHeight="1">
       <c r="A7" s="4" t="s">
@@ -6528,23 +6499,23 @@
       <c r="BM7" s="11"/>
       <c r="BN7" s="5"/>
       <c r="BO7" s="5"/>
-      <c r="BP7" s="154" t="s">
+      <c r="BP7" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ7" s="155"/>
-      <c r="BR7" s="156"/>
-      <c r="BS7" s="163">
+      <c r="BQ7" s="122"/>
+      <c r="BR7" s="123"/>
+      <c r="BS7" s="130">
         <v>45583</v>
       </c>
-      <c r="BT7" s="164"/>
-      <c r="BU7" s="164"/>
-      <c r="BV7" s="165"/>
-      <c r="BW7" s="154" t="s">
+      <c r="BT7" s="131"/>
+      <c r="BU7" s="131"/>
+      <c r="BV7" s="132"/>
+      <c r="BW7" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX7" s="155"/>
-      <c r="BY7" s="155"/>
-      <c r="BZ7" s="156"/>
+      <c r="BX7" s="122"/>
+      <c r="BY7" s="122"/>
+      <c r="BZ7" s="123"/>
     </row>
     <row r="8" spans="1:78" ht="18.75" customHeight="1">
       <c r="A8" s="14"/>
@@ -6618,17 +6589,17 @@
       <c r="BM8" s="21"/>
       <c r="BN8" s="15"/>
       <c r="BO8" s="15"/>
-      <c r="BP8" s="157"/>
-      <c r="BQ8" s="158"/>
-      <c r="BR8" s="159"/>
-      <c r="BS8" s="166"/>
-      <c r="BT8" s="167"/>
-      <c r="BU8" s="167"/>
-      <c r="BV8" s="168"/>
-      <c r="BW8" s="157"/>
-      <c r="BX8" s="158"/>
-      <c r="BY8" s="158"/>
-      <c r="BZ8" s="159"/>
+      <c r="BP8" s="124"/>
+      <c r="BQ8" s="125"/>
+      <c r="BR8" s="126"/>
+      <c r="BS8" s="133"/>
+      <c r="BT8" s="134"/>
+      <c r="BU8" s="134"/>
+      <c r="BV8" s="135"/>
+      <c r="BW8" s="124"/>
+      <c r="BX8" s="125"/>
+      <c r="BY8" s="125"/>
+      <c r="BZ8" s="126"/>
     </row>
     <row r="9" spans="1:78" ht="18.75" customHeight="1">
       <c r="A9" s="14"/>
@@ -6700,17 +6671,17 @@
       <c r="BM9" s="21"/>
       <c r="BN9" s="15"/>
       <c r="BO9" s="15"/>
-      <c r="BP9" s="160"/>
-      <c r="BQ9" s="161"/>
-      <c r="BR9" s="162"/>
-      <c r="BS9" s="169"/>
-      <c r="BT9" s="170"/>
-      <c r="BU9" s="170"/>
-      <c r="BV9" s="171"/>
-      <c r="BW9" s="160"/>
-      <c r="BX9" s="161"/>
-      <c r="BY9" s="161"/>
-      <c r="BZ9" s="162"/>
+      <c r="BP9" s="127"/>
+      <c r="BQ9" s="128"/>
+      <c r="BR9" s="129"/>
+      <c r="BS9" s="136"/>
+      <c r="BT9" s="137"/>
+      <c r="BU9" s="137"/>
+      <c r="BV9" s="138"/>
+      <c r="BW9" s="127"/>
+      <c r="BX9" s="128"/>
+      <c r="BY9" s="128"/>
+      <c r="BZ9" s="129"/>
     </row>
     <row r="10" spans="1:78" ht="18.75" customHeight="1">
       <c r="A10" s="4" t="s">
@@ -6798,23 +6769,23 @@
       <c r="BM10" s="11"/>
       <c r="BN10" s="5"/>
       <c r="BO10" s="5"/>
-      <c r="BP10" s="154" t="s">
+      <c r="BP10" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ10" s="155"/>
-      <c r="BR10" s="156"/>
-      <c r="BS10" s="163">
+      <c r="BQ10" s="122"/>
+      <c r="BR10" s="123"/>
+      <c r="BS10" s="130">
         <v>45583</v>
       </c>
-      <c r="BT10" s="164"/>
-      <c r="BU10" s="164"/>
-      <c r="BV10" s="165"/>
-      <c r="BW10" s="154" t="s">
+      <c r="BT10" s="131"/>
+      <c r="BU10" s="131"/>
+      <c r="BV10" s="132"/>
+      <c r="BW10" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX10" s="155"/>
-      <c r="BY10" s="155"/>
-      <c r="BZ10" s="156"/>
+      <c r="BX10" s="122"/>
+      <c r="BY10" s="122"/>
+      <c r="BZ10" s="123"/>
     </row>
     <row r="11" spans="1:78" ht="18.75" customHeight="1">
       <c r="A11" s="14"/>
@@ -6889,17 +6860,17 @@
       <c r="BM11" s="21"/>
       <c r="BN11" s="15"/>
       <c r="BO11" s="15"/>
-      <c r="BP11" s="157"/>
-      <c r="BQ11" s="158"/>
-      <c r="BR11" s="159"/>
-      <c r="BS11" s="166"/>
-      <c r="BT11" s="167"/>
-      <c r="BU11" s="167"/>
-      <c r="BV11" s="168"/>
-      <c r="BW11" s="157"/>
-      <c r="BX11" s="158"/>
-      <c r="BY11" s="158"/>
-      <c r="BZ11" s="159"/>
+      <c r="BP11" s="124"/>
+      <c r="BQ11" s="125"/>
+      <c r="BR11" s="126"/>
+      <c r="BS11" s="133"/>
+      <c r="BT11" s="134"/>
+      <c r="BU11" s="134"/>
+      <c r="BV11" s="135"/>
+      <c r="BW11" s="124"/>
+      <c r="BX11" s="125"/>
+      <c r="BY11" s="125"/>
+      <c r="BZ11" s="126"/>
     </row>
     <row r="12" spans="1:78" ht="18.75" customHeight="1">
       <c r="A12" s="14"/>
@@ -6971,17 +6942,17 @@
       <c r="BM12" s="21"/>
       <c r="BN12" s="15"/>
       <c r="BO12" s="15"/>
-      <c r="BP12" s="157"/>
-      <c r="BQ12" s="158"/>
-      <c r="BR12" s="159"/>
-      <c r="BS12" s="166"/>
-      <c r="BT12" s="167"/>
-      <c r="BU12" s="167"/>
-      <c r="BV12" s="168"/>
-      <c r="BW12" s="157"/>
-      <c r="BX12" s="158"/>
-      <c r="BY12" s="158"/>
-      <c r="BZ12" s="159"/>
+      <c r="BP12" s="124"/>
+      <c r="BQ12" s="125"/>
+      <c r="BR12" s="126"/>
+      <c r="BS12" s="133"/>
+      <c r="BT12" s="134"/>
+      <c r="BU12" s="134"/>
+      <c r="BV12" s="135"/>
+      <c r="BW12" s="124"/>
+      <c r="BX12" s="125"/>
+      <c r="BY12" s="125"/>
+      <c r="BZ12" s="126"/>
     </row>
     <row r="13" spans="1:78" ht="18.75" customHeight="1">
       <c r="A13" s="14"/>
@@ -7053,17 +7024,17 @@
       <c r="BM13" s="21"/>
       <c r="BN13" s="15"/>
       <c r="BO13" s="15"/>
-      <c r="BP13" s="160"/>
-      <c r="BQ13" s="161"/>
-      <c r="BR13" s="162"/>
-      <c r="BS13" s="169"/>
-      <c r="BT13" s="170"/>
-      <c r="BU13" s="170"/>
-      <c r="BV13" s="171"/>
-      <c r="BW13" s="160"/>
-      <c r="BX13" s="161"/>
-      <c r="BY13" s="161"/>
-      <c r="BZ13" s="162"/>
+      <c r="BP13" s="127"/>
+      <c r="BQ13" s="128"/>
+      <c r="BR13" s="129"/>
+      <c r="BS13" s="136"/>
+      <c r="BT13" s="137"/>
+      <c r="BU13" s="137"/>
+      <c r="BV13" s="138"/>
+      <c r="BW13" s="127"/>
+      <c r="BX13" s="128"/>
+      <c r="BY13" s="128"/>
+      <c r="BZ13" s="129"/>
     </row>
     <row r="14" spans="1:78" s="19" customFormat="1" ht="18.75" customHeight="1">
       <c r="A14" s="4" t="s">
@@ -7151,23 +7122,23 @@
       <c r="BM14" s="9"/>
       <c r="BN14" s="9"/>
       <c r="BO14" s="9"/>
-      <c r="BP14" s="154" t="s">
+      <c r="BP14" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ14" s="155"/>
-      <c r="BR14" s="156"/>
-      <c r="BS14" s="163">
+      <c r="BQ14" s="122"/>
+      <c r="BR14" s="123"/>
+      <c r="BS14" s="130">
         <v>45583</v>
       </c>
-      <c r="BT14" s="164"/>
-      <c r="BU14" s="164"/>
-      <c r="BV14" s="165"/>
-      <c r="BW14" s="154" t="s">
+      <c r="BT14" s="131"/>
+      <c r="BU14" s="131"/>
+      <c r="BV14" s="132"/>
+      <c r="BW14" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX14" s="155"/>
-      <c r="BY14" s="155"/>
-      <c r="BZ14" s="156"/>
+      <c r="BX14" s="122"/>
+      <c r="BY14" s="122"/>
+      <c r="BZ14" s="123"/>
     </row>
     <row r="15" spans="1:78" s="19" customFormat="1" ht="18.75" customHeight="1">
       <c r="A15" s="14"/>
@@ -7191,17 +7162,17 @@
       <c r="BE15" s="24"/>
       <c r="BF15" s="22"/>
       <c r="BG15" s="21"/>
-      <c r="BP15" s="157"/>
-      <c r="BQ15" s="158"/>
-      <c r="BR15" s="159"/>
-      <c r="BS15" s="166"/>
-      <c r="BT15" s="167"/>
-      <c r="BU15" s="167"/>
-      <c r="BV15" s="168"/>
-      <c r="BW15" s="157"/>
-      <c r="BX15" s="158"/>
-      <c r="BY15" s="158"/>
-      <c r="BZ15" s="159"/>
+      <c r="BP15" s="124"/>
+      <c r="BQ15" s="125"/>
+      <c r="BR15" s="126"/>
+      <c r="BS15" s="133"/>
+      <c r="BT15" s="134"/>
+      <c r="BU15" s="134"/>
+      <c r="BV15" s="135"/>
+      <c r="BW15" s="124"/>
+      <c r="BX15" s="125"/>
+      <c r="BY15" s="125"/>
+      <c r="BZ15" s="126"/>
     </row>
     <row r="16" spans="1:78" s="19" customFormat="1" ht="18.75" customHeight="1">
       <c r="A16" s="14"/>
@@ -7221,17 +7192,17 @@
       <c r="BE16" s="24"/>
       <c r="BF16" s="22"/>
       <c r="BG16" s="21"/>
-      <c r="BP16" s="157"/>
-      <c r="BQ16" s="158"/>
-      <c r="BR16" s="159"/>
-      <c r="BS16" s="166"/>
-      <c r="BT16" s="167"/>
-      <c r="BU16" s="167"/>
-      <c r="BV16" s="168"/>
-      <c r="BW16" s="157"/>
-      <c r="BX16" s="158"/>
-      <c r="BY16" s="158"/>
-      <c r="BZ16" s="159"/>
+      <c r="BP16" s="124"/>
+      <c r="BQ16" s="125"/>
+      <c r="BR16" s="126"/>
+      <c r="BS16" s="133"/>
+      <c r="BT16" s="134"/>
+      <c r="BU16" s="134"/>
+      <c r="BV16" s="135"/>
+      <c r="BW16" s="124"/>
+      <c r="BX16" s="125"/>
+      <c r="BY16" s="125"/>
+      <c r="BZ16" s="126"/>
     </row>
     <row r="17" spans="1:78" s="19" customFormat="1" ht="18.75" customHeight="1">
       <c r="A17" s="14"/>
@@ -7251,17 +7222,17 @@
       <c r="BE17" s="24"/>
       <c r="BF17" s="22"/>
       <c r="BG17" s="21"/>
-      <c r="BP17" s="160"/>
-      <c r="BQ17" s="161"/>
-      <c r="BR17" s="162"/>
-      <c r="BS17" s="169"/>
-      <c r="BT17" s="170"/>
-      <c r="BU17" s="170"/>
-      <c r="BV17" s="171"/>
-      <c r="BW17" s="160"/>
-      <c r="BX17" s="161"/>
-      <c r="BY17" s="161"/>
-      <c r="BZ17" s="162"/>
+      <c r="BP17" s="127"/>
+      <c r="BQ17" s="128"/>
+      <c r="BR17" s="129"/>
+      <c r="BS17" s="136"/>
+      <c r="BT17" s="137"/>
+      <c r="BU17" s="137"/>
+      <c r="BV17" s="138"/>
+      <c r="BW17" s="127"/>
+      <c r="BX17" s="128"/>
+      <c r="BY17" s="128"/>
+      <c r="BZ17" s="129"/>
     </row>
     <row r="18" spans="1:78" ht="18.75" customHeight="1">
       <c r="A18" s="4" t="s">
@@ -7349,23 +7320,23 @@
       <c r="BM18" s="9"/>
       <c r="BN18" s="9"/>
       <c r="BO18" s="9"/>
-      <c r="BP18" s="154" t="s">
+      <c r="BP18" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ18" s="155"/>
-      <c r="BR18" s="156"/>
-      <c r="BS18" s="163">
+      <c r="BQ18" s="122"/>
+      <c r="BR18" s="123"/>
+      <c r="BS18" s="130">
         <v>45583</v>
       </c>
-      <c r="BT18" s="164"/>
-      <c r="BU18" s="164"/>
-      <c r="BV18" s="165"/>
-      <c r="BW18" s="154" t="s">
+      <c r="BT18" s="131"/>
+      <c r="BU18" s="131"/>
+      <c r="BV18" s="132"/>
+      <c r="BW18" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX18" s="155"/>
-      <c r="BY18" s="155"/>
-      <c r="BZ18" s="156"/>
+      <c r="BX18" s="122"/>
+      <c r="BY18" s="122"/>
+      <c r="BZ18" s="123"/>
     </row>
     <row r="19" spans="1:78" ht="18.75" customHeight="1">
       <c r="A19" s="14"/>
@@ -7441,17 +7412,17 @@
       <c r="BM19" s="19"/>
       <c r="BN19" s="19"/>
       <c r="BO19" s="19"/>
-      <c r="BP19" s="157"/>
-      <c r="BQ19" s="158"/>
-      <c r="BR19" s="159"/>
-      <c r="BS19" s="166"/>
-      <c r="BT19" s="167"/>
-      <c r="BU19" s="167"/>
-      <c r="BV19" s="168"/>
-      <c r="BW19" s="157"/>
-      <c r="BX19" s="158"/>
-      <c r="BY19" s="158"/>
-      <c r="BZ19" s="159"/>
+      <c r="BP19" s="124"/>
+      <c r="BQ19" s="125"/>
+      <c r="BR19" s="126"/>
+      <c r="BS19" s="133"/>
+      <c r="BT19" s="134"/>
+      <c r="BU19" s="134"/>
+      <c r="BV19" s="135"/>
+      <c r="BW19" s="124"/>
+      <c r="BX19" s="125"/>
+      <c r="BY19" s="125"/>
+      <c r="BZ19" s="126"/>
     </row>
     <row r="20" spans="1:78" ht="18.75" customHeight="1">
       <c r="A20" s="14"/>
@@ -7523,17 +7494,17 @@
       <c r="BM20" s="19"/>
       <c r="BN20" s="19"/>
       <c r="BO20" s="19"/>
-      <c r="BP20" s="157"/>
-      <c r="BQ20" s="158"/>
-      <c r="BR20" s="159"/>
-      <c r="BS20" s="166"/>
-      <c r="BT20" s="167"/>
-      <c r="BU20" s="167"/>
-      <c r="BV20" s="168"/>
-      <c r="BW20" s="157"/>
-      <c r="BX20" s="158"/>
-      <c r="BY20" s="158"/>
-      <c r="BZ20" s="159"/>
+      <c r="BP20" s="124"/>
+      <c r="BQ20" s="125"/>
+      <c r="BR20" s="126"/>
+      <c r="BS20" s="133"/>
+      <c r="BT20" s="134"/>
+      <c r="BU20" s="134"/>
+      <c r="BV20" s="135"/>
+      <c r="BW20" s="124"/>
+      <c r="BX20" s="125"/>
+      <c r="BY20" s="125"/>
+      <c r="BZ20" s="126"/>
     </row>
     <row r="21" spans="1:78" ht="18.75" customHeight="1">
       <c r="A21" s="14"/>
@@ -7605,17 +7576,17 @@
       <c r="BM21" s="19"/>
       <c r="BN21" s="19"/>
       <c r="BO21" s="19"/>
-      <c r="BP21" s="160"/>
-      <c r="BQ21" s="161"/>
-      <c r="BR21" s="162"/>
-      <c r="BS21" s="169"/>
-      <c r="BT21" s="170"/>
-      <c r="BU21" s="170"/>
-      <c r="BV21" s="171"/>
-      <c r="BW21" s="160"/>
-      <c r="BX21" s="161"/>
-      <c r="BY21" s="161"/>
-      <c r="BZ21" s="162"/>
+      <c r="BP21" s="127"/>
+      <c r="BQ21" s="128"/>
+      <c r="BR21" s="129"/>
+      <c r="BS21" s="136"/>
+      <c r="BT21" s="137"/>
+      <c r="BU21" s="137"/>
+      <c r="BV21" s="138"/>
+      <c r="BW21" s="127"/>
+      <c r="BX21" s="128"/>
+      <c r="BY21" s="128"/>
+      <c r="BZ21" s="129"/>
     </row>
     <row r="22" spans="1:78" ht="18.75" customHeight="1">
       <c r="A22" s="4" t="s">
@@ -7703,23 +7674,23 @@
       <c r="BM22" s="11"/>
       <c r="BN22" s="5"/>
       <c r="BO22" s="5"/>
-      <c r="BP22" s="154" t="s">
+      <c r="BP22" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ22" s="155"/>
-      <c r="BR22" s="156"/>
-      <c r="BS22" s="163">
+      <c r="BQ22" s="122"/>
+      <c r="BR22" s="123"/>
+      <c r="BS22" s="130">
         <v>45583</v>
       </c>
-      <c r="BT22" s="164"/>
-      <c r="BU22" s="164"/>
-      <c r="BV22" s="165"/>
-      <c r="BW22" s="154" t="s">
+      <c r="BT22" s="131"/>
+      <c r="BU22" s="131"/>
+      <c r="BV22" s="132"/>
+      <c r="BW22" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX22" s="155"/>
-      <c r="BY22" s="155"/>
-      <c r="BZ22" s="156"/>
+      <c r="BX22" s="122"/>
+      <c r="BY22" s="122"/>
+      <c r="BZ22" s="123"/>
     </row>
     <row r="23" spans="1:78" ht="18.75" customHeight="1">
       <c r="A23" s="14"/>
@@ -7795,17 +7766,17 @@
       <c r="BM23" s="21"/>
       <c r="BN23" s="15"/>
       <c r="BO23" s="15"/>
-      <c r="BP23" s="157"/>
-      <c r="BQ23" s="158"/>
-      <c r="BR23" s="159"/>
-      <c r="BS23" s="166"/>
-      <c r="BT23" s="167"/>
-      <c r="BU23" s="167"/>
-      <c r="BV23" s="168"/>
-      <c r="BW23" s="157"/>
-      <c r="BX23" s="158"/>
-      <c r="BY23" s="158"/>
-      <c r="BZ23" s="159"/>
+      <c r="BP23" s="124"/>
+      <c r="BQ23" s="125"/>
+      <c r="BR23" s="126"/>
+      <c r="BS23" s="133"/>
+      <c r="BT23" s="134"/>
+      <c r="BU23" s="134"/>
+      <c r="BV23" s="135"/>
+      <c r="BW23" s="124"/>
+      <c r="BX23" s="125"/>
+      <c r="BY23" s="125"/>
+      <c r="BZ23" s="126"/>
     </row>
     <row r="24" spans="1:78" ht="18.75" customHeight="1">
       <c r="A24" s="14"/>
@@ -7877,17 +7848,17 @@
       <c r="BM24" s="21"/>
       <c r="BN24" s="15"/>
       <c r="BO24" s="15"/>
-      <c r="BP24" s="157"/>
-      <c r="BQ24" s="158"/>
-      <c r="BR24" s="159"/>
-      <c r="BS24" s="166"/>
-      <c r="BT24" s="167"/>
-      <c r="BU24" s="167"/>
-      <c r="BV24" s="168"/>
-      <c r="BW24" s="157"/>
-      <c r="BX24" s="158"/>
-      <c r="BY24" s="158"/>
-      <c r="BZ24" s="159"/>
+      <c r="BP24" s="124"/>
+      <c r="BQ24" s="125"/>
+      <c r="BR24" s="126"/>
+      <c r="BS24" s="133"/>
+      <c r="BT24" s="134"/>
+      <c r="BU24" s="134"/>
+      <c r="BV24" s="135"/>
+      <c r="BW24" s="124"/>
+      <c r="BX24" s="125"/>
+      <c r="BY24" s="125"/>
+      <c r="BZ24" s="126"/>
     </row>
     <row r="25" spans="1:78" ht="18.75" customHeight="1">
       <c r="A25" s="14"/>
@@ -7959,17 +7930,17 @@
       <c r="BM25" s="21"/>
       <c r="BN25" s="15"/>
       <c r="BO25" s="15"/>
-      <c r="BP25" s="160"/>
-      <c r="BQ25" s="161"/>
-      <c r="BR25" s="162"/>
-      <c r="BS25" s="169"/>
-      <c r="BT25" s="170"/>
-      <c r="BU25" s="170"/>
-      <c r="BV25" s="171"/>
-      <c r="BW25" s="160"/>
-      <c r="BX25" s="161"/>
-      <c r="BY25" s="161"/>
-      <c r="BZ25" s="162"/>
+      <c r="BP25" s="127"/>
+      <c r="BQ25" s="128"/>
+      <c r="BR25" s="129"/>
+      <c r="BS25" s="136"/>
+      <c r="BT25" s="137"/>
+      <c r="BU25" s="137"/>
+      <c r="BV25" s="138"/>
+      <c r="BW25" s="127"/>
+      <c r="BX25" s="128"/>
+      <c r="BY25" s="128"/>
+      <c r="BZ25" s="129"/>
     </row>
     <row r="26" spans="1:78" ht="18.75" customHeight="1">
       <c r="A26" s="4" t="s">
@@ -8057,23 +8028,23 @@
       <c r="BM26" s="11"/>
       <c r="BN26" s="5"/>
       <c r="BO26" s="5"/>
-      <c r="BP26" s="154" t="s">
+      <c r="BP26" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ26" s="155"/>
-      <c r="BR26" s="156"/>
-      <c r="BS26" s="163">
+      <c r="BQ26" s="122"/>
+      <c r="BR26" s="123"/>
+      <c r="BS26" s="130">
         <v>45583</v>
       </c>
-      <c r="BT26" s="164"/>
-      <c r="BU26" s="164"/>
-      <c r="BV26" s="165"/>
-      <c r="BW26" s="154" t="s">
+      <c r="BT26" s="131"/>
+      <c r="BU26" s="131"/>
+      <c r="BV26" s="132"/>
+      <c r="BW26" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX26" s="155"/>
-      <c r="BY26" s="155"/>
-      <c r="BZ26" s="156"/>
+      <c r="BX26" s="122"/>
+      <c r="BY26" s="122"/>
+      <c r="BZ26" s="123"/>
     </row>
     <row r="27" spans="1:78" ht="18.75" customHeight="1">
       <c r="A27" s="14"/>
@@ -8149,17 +8120,17 @@
       <c r="BM27" s="21"/>
       <c r="BN27" s="15"/>
       <c r="BO27" s="15"/>
-      <c r="BP27" s="157"/>
-      <c r="BQ27" s="158"/>
-      <c r="BR27" s="159"/>
-      <c r="BS27" s="166"/>
-      <c r="BT27" s="167"/>
-      <c r="BU27" s="167"/>
-      <c r="BV27" s="168"/>
-      <c r="BW27" s="157"/>
-      <c r="BX27" s="158"/>
-      <c r="BY27" s="158"/>
-      <c r="BZ27" s="159"/>
+      <c r="BP27" s="124"/>
+      <c r="BQ27" s="125"/>
+      <c r="BR27" s="126"/>
+      <c r="BS27" s="133"/>
+      <c r="BT27" s="134"/>
+      <c r="BU27" s="134"/>
+      <c r="BV27" s="135"/>
+      <c r="BW27" s="124"/>
+      <c r="BX27" s="125"/>
+      <c r="BY27" s="125"/>
+      <c r="BZ27" s="126"/>
     </row>
     <row r="28" spans="1:78" ht="18.75" customHeight="1">
       <c r="A28" s="14"/>
@@ -8231,17 +8202,17 @@
       <c r="BM28" s="21"/>
       <c r="BN28" s="15"/>
       <c r="BO28" s="15"/>
-      <c r="BP28" s="157"/>
-      <c r="BQ28" s="158"/>
-      <c r="BR28" s="159"/>
-      <c r="BS28" s="166"/>
-      <c r="BT28" s="167"/>
-      <c r="BU28" s="167"/>
-      <c r="BV28" s="168"/>
-      <c r="BW28" s="157"/>
-      <c r="BX28" s="158"/>
-      <c r="BY28" s="158"/>
-      <c r="BZ28" s="159"/>
+      <c r="BP28" s="124"/>
+      <c r="BQ28" s="125"/>
+      <c r="BR28" s="126"/>
+      <c r="BS28" s="133"/>
+      <c r="BT28" s="134"/>
+      <c r="BU28" s="134"/>
+      <c r="BV28" s="135"/>
+      <c r="BW28" s="124"/>
+      <c r="BX28" s="125"/>
+      <c r="BY28" s="125"/>
+      <c r="BZ28" s="126"/>
     </row>
     <row r="29" spans="1:78" ht="18.75" customHeight="1">
       <c r="A29" s="14"/>
@@ -8313,17 +8284,17 @@
       <c r="BM29" s="21"/>
       <c r="BN29" s="15"/>
       <c r="BO29" s="15"/>
-      <c r="BP29" s="160"/>
-      <c r="BQ29" s="161"/>
-      <c r="BR29" s="162"/>
-      <c r="BS29" s="169"/>
-      <c r="BT29" s="170"/>
-      <c r="BU29" s="170"/>
-      <c r="BV29" s="171"/>
-      <c r="BW29" s="160"/>
-      <c r="BX29" s="161"/>
-      <c r="BY29" s="161"/>
-      <c r="BZ29" s="162"/>
+      <c r="BP29" s="127"/>
+      <c r="BQ29" s="128"/>
+      <c r="BR29" s="129"/>
+      <c r="BS29" s="136"/>
+      <c r="BT29" s="137"/>
+      <c r="BU29" s="137"/>
+      <c r="BV29" s="138"/>
+      <c r="BW29" s="127"/>
+      <c r="BX29" s="128"/>
+      <c r="BY29" s="128"/>
+      <c r="BZ29" s="129"/>
     </row>
     <row r="30" spans="1:78" ht="18.75" customHeight="1">
       <c r="A30" s="4" t="s">
@@ -8411,23 +8382,23 @@
       <c r="BM30" s="11"/>
       <c r="BN30" s="5"/>
       <c r="BO30" s="5"/>
-      <c r="BP30" s="154" t="s">
+      <c r="BP30" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ30" s="155"/>
-      <c r="BR30" s="156"/>
-      <c r="BS30" s="163">
+      <c r="BQ30" s="122"/>
+      <c r="BR30" s="123"/>
+      <c r="BS30" s="130">
         <v>45583</v>
       </c>
-      <c r="BT30" s="164"/>
-      <c r="BU30" s="164"/>
-      <c r="BV30" s="165"/>
-      <c r="BW30" s="154" t="s">
+      <c r="BT30" s="131"/>
+      <c r="BU30" s="131"/>
+      <c r="BV30" s="132"/>
+      <c r="BW30" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX30" s="155"/>
-      <c r="BY30" s="155"/>
-      <c r="BZ30" s="156"/>
+      <c r="BX30" s="122"/>
+      <c r="BY30" s="122"/>
+      <c r="BZ30" s="123"/>
     </row>
     <row r="31" spans="1:78" ht="18.75" customHeight="1">
       <c r="A31" s="14"/>
@@ -8503,17 +8474,17 @@
       <c r="BM31" s="21"/>
       <c r="BN31" s="15"/>
       <c r="BO31" s="15"/>
-      <c r="BP31" s="157"/>
-      <c r="BQ31" s="158"/>
-      <c r="BR31" s="159"/>
-      <c r="BS31" s="166"/>
-      <c r="BT31" s="167"/>
-      <c r="BU31" s="167"/>
-      <c r="BV31" s="168"/>
-      <c r="BW31" s="157"/>
-      <c r="BX31" s="158"/>
-      <c r="BY31" s="158"/>
-      <c r="BZ31" s="159"/>
+      <c r="BP31" s="124"/>
+      <c r="BQ31" s="125"/>
+      <c r="BR31" s="126"/>
+      <c r="BS31" s="133"/>
+      <c r="BT31" s="134"/>
+      <c r="BU31" s="134"/>
+      <c r="BV31" s="135"/>
+      <c r="BW31" s="124"/>
+      <c r="BX31" s="125"/>
+      <c r="BY31" s="125"/>
+      <c r="BZ31" s="126"/>
     </row>
     <row r="32" spans="1:78" ht="18.75" customHeight="1">
       <c r="A32" s="14"/>
@@ -8585,17 +8556,17 @@
       <c r="BM32" s="21"/>
       <c r="BN32" s="15"/>
       <c r="BO32" s="15"/>
-      <c r="BP32" s="157"/>
-      <c r="BQ32" s="158"/>
-      <c r="BR32" s="159"/>
-      <c r="BS32" s="166"/>
-      <c r="BT32" s="167"/>
-      <c r="BU32" s="167"/>
-      <c r="BV32" s="168"/>
-      <c r="BW32" s="157"/>
-      <c r="BX32" s="158"/>
-      <c r="BY32" s="158"/>
-      <c r="BZ32" s="159"/>
+      <c r="BP32" s="124"/>
+      <c r="BQ32" s="125"/>
+      <c r="BR32" s="126"/>
+      <c r="BS32" s="133"/>
+      <c r="BT32" s="134"/>
+      <c r="BU32" s="134"/>
+      <c r="BV32" s="135"/>
+      <c r="BW32" s="124"/>
+      <c r="BX32" s="125"/>
+      <c r="BY32" s="125"/>
+      <c r="BZ32" s="126"/>
     </row>
     <row r="33" spans="1:78" ht="18.75" customHeight="1">
       <c r="A33" s="25"/>
@@ -8667,17 +8638,17 @@
       <c r="BM33" s="30"/>
       <c r="BN33" s="26"/>
       <c r="BO33" s="26"/>
-      <c r="BP33" s="160"/>
-      <c r="BQ33" s="161"/>
-      <c r="BR33" s="162"/>
-      <c r="BS33" s="169"/>
-      <c r="BT33" s="170"/>
-      <c r="BU33" s="170"/>
-      <c r="BV33" s="171"/>
-      <c r="BW33" s="160"/>
-      <c r="BX33" s="161"/>
-      <c r="BY33" s="161"/>
-      <c r="BZ33" s="162"/>
+      <c r="BP33" s="127"/>
+      <c r="BQ33" s="128"/>
+      <c r="BR33" s="129"/>
+      <c r="BS33" s="136"/>
+      <c r="BT33" s="137"/>
+      <c r="BU33" s="137"/>
+      <c r="BV33" s="138"/>
+      <c r="BW33" s="127"/>
+      <c r="BX33" s="128"/>
+      <c r="BY33" s="128"/>
+      <c r="BZ33" s="129"/>
     </row>
     <row r="34" spans="1:78" ht="18.75" customHeight="1">
       <c r="A34" s="14" t="s">
@@ -8765,23 +8736,23 @@
       <c r="BM34" s="21"/>
       <c r="BN34" s="15"/>
       <c r="BO34" s="15"/>
-      <c r="BP34" s="154" t="s">
+      <c r="BP34" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ34" s="155"/>
-      <c r="BR34" s="156"/>
-      <c r="BS34" s="163">
+      <c r="BQ34" s="122"/>
+      <c r="BR34" s="123"/>
+      <c r="BS34" s="130">
         <v>45583</v>
       </c>
-      <c r="BT34" s="164"/>
-      <c r="BU34" s="164"/>
-      <c r="BV34" s="165"/>
-      <c r="BW34" s="154" t="s">
+      <c r="BT34" s="131"/>
+      <c r="BU34" s="131"/>
+      <c r="BV34" s="132"/>
+      <c r="BW34" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX34" s="155"/>
-      <c r="BY34" s="155"/>
-      <c r="BZ34" s="156"/>
+      <c r="BX34" s="122"/>
+      <c r="BY34" s="122"/>
+      <c r="BZ34" s="123"/>
     </row>
     <row r="35" spans="1:78" ht="18.75" customHeight="1">
       <c r="A35" s="14"/>
@@ -8857,17 +8828,17 @@
       <c r="BM35" s="21"/>
       <c r="BN35" s="15"/>
       <c r="BO35" s="15"/>
-      <c r="BP35" s="157"/>
-      <c r="BQ35" s="158"/>
-      <c r="BR35" s="159"/>
-      <c r="BS35" s="166"/>
-      <c r="BT35" s="167"/>
-      <c r="BU35" s="167"/>
-      <c r="BV35" s="168"/>
-      <c r="BW35" s="157"/>
-      <c r="BX35" s="158"/>
-      <c r="BY35" s="158"/>
-      <c r="BZ35" s="159"/>
+      <c r="BP35" s="124"/>
+      <c r="BQ35" s="125"/>
+      <c r="BR35" s="126"/>
+      <c r="BS35" s="133"/>
+      <c r="BT35" s="134"/>
+      <c r="BU35" s="134"/>
+      <c r="BV35" s="135"/>
+      <c r="BW35" s="124"/>
+      <c r="BX35" s="125"/>
+      <c r="BY35" s="125"/>
+      <c r="BZ35" s="126"/>
     </row>
     <row r="36" spans="1:78" ht="18.75" customHeight="1">
       <c r="A36" s="14"/>
@@ -8939,17 +8910,17 @@
       <c r="BM36" s="21"/>
       <c r="BN36" s="15"/>
       <c r="BO36" s="15"/>
-      <c r="BP36" s="157"/>
-      <c r="BQ36" s="158"/>
-      <c r="BR36" s="159"/>
-      <c r="BS36" s="166"/>
-      <c r="BT36" s="167"/>
-      <c r="BU36" s="167"/>
-      <c r="BV36" s="168"/>
-      <c r="BW36" s="157"/>
-      <c r="BX36" s="158"/>
-      <c r="BY36" s="158"/>
-      <c r="BZ36" s="159"/>
+      <c r="BP36" s="124"/>
+      <c r="BQ36" s="125"/>
+      <c r="BR36" s="126"/>
+      <c r="BS36" s="133"/>
+      <c r="BT36" s="134"/>
+      <c r="BU36" s="134"/>
+      <c r="BV36" s="135"/>
+      <c r="BW36" s="124"/>
+      <c r="BX36" s="125"/>
+      <c r="BY36" s="125"/>
+      <c r="BZ36" s="126"/>
     </row>
     <row r="37" spans="1:78" ht="18.75" customHeight="1">
       <c r="A37" s="25"/>
@@ -9021,17 +8992,17 @@
       <c r="BM37" s="30"/>
       <c r="BN37" s="26"/>
       <c r="BO37" s="26"/>
-      <c r="BP37" s="160"/>
-      <c r="BQ37" s="161"/>
-      <c r="BR37" s="162"/>
-      <c r="BS37" s="169"/>
-      <c r="BT37" s="170"/>
-      <c r="BU37" s="170"/>
-      <c r="BV37" s="171"/>
-      <c r="BW37" s="160"/>
-      <c r="BX37" s="161"/>
-      <c r="BY37" s="161"/>
-      <c r="BZ37" s="162"/>
+      <c r="BP37" s="127"/>
+      <c r="BQ37" s="128"/>
+      <c r="BR37" s="129"/>
+      <c r="BS37" s="136"/>
+      <c r="BT37" s="137"/>
+      <c r="BU37" s="137"/>
+      <c r="BV37" s="138"/>
+      <c r="BW37" s="127"/>
+      <c r="BX37" s="128"/>
+      <c r="BY37" s="128"/>
+      <c r="BZ37" s="129"/>
     </row>
     <row r="38" spans="1:78" ht="18.75" customHeight="1">
       <c r="A38" s="14" t="s">
@@ -9119,23 +9090,23 @@
       <c r="BM38" s="21"/>
       <c r="BN38" s="15"/>
       <c r="BO38" s="15"/>
-      <c r="BP38" s="154" t="s">
+      <c r="BP38" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ38" s="155"/>
-      <c r="BR38" s="156"/>
-      <c r="BS38" s="163">
+      <c r="BQ38" s="122"/>
+      <c r="BR38" s="123"/>
+      <c r="BS38" s="130">
         <v>45583</v>
       </c>
-      <c r="BT38" s="164"/>
-      <c r="BU38" s="164"/>
-      <c r="BV38" s="165"/>
-      <c r="BW38" s="154" t="s">
+      <c r="BT38" s="131"/>
+      <c r="BU38" s="131"/>
+      <c r="BV38" s="132"/>
+      <c r="BW38" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX38" s="155"/>
-      <c r="BY38" s="155"/>
-      <c r="BZ38" s="156"/>
+      <c r="BX38" s="122"/>
+      <c r="BY38" s="122"/>
+      <c r="BZ38" s="123"/>
     </row>
     <row r="39" spans="1:78" ht="18.75" customHeight="1">
       <c r="A39" s="14"/>
@@ -9211,17 +9182,17 @@
       <c r="BM39" s="21"/>
       <c r="BN39" s="15"/>
       <c r="BO39" s="15"/>
-      <c r="BP39" s="157"/>
-      <c r="BQ39" s="158"/>
-      <c r="BR39" s="159"/>
-      <c r="BS39" s="166"/>
-      <c r="BT39" s="167"/>
-      <c r="BU39" s="167"/>
-      <c r="BV39" s="168"/>
-      <c r="BW39" s="157"/>
-      <c r="BX39" s="158"/>
-      <c r="BY39" s="158"/>
-      <c r="BZ39" s="159"/>
+      <c r="BP39" s="124"/>
+      <c r="BQ39" s="125"/>
+      <c r="BR39" s="126"/>
+      <c r="BS39" s="133"/>
+      <c r="BT39" s="134"/>
+      <c r="BU39" s="134"/>
+      <c r="BV39" s="135"/>
+      <c r="BW39" s="124"/>
+      <c r="BX39" s="125"/>
+      <c r="BY39" s="125"/>
+      <c r="BZ39" s="126"/>
     </row>
     <row r="40" spans="1:78" ht="18.75" customHeight="1">
       <c r="A40" s="14"/>
@@ -9293,17 +9264,17 @@
       <c r="BM40" s="21"/>
       <c r="BN40" s="15"/>
       <c r="BO40" s="15"/>
-      <c r="BP40" s="157"/>
-      <c r="BQ40" s="158"/>
-      <c r="BR40" s="159"/>
-      <c r="BS40" s="166"/>
-      <c r="BT40" s="167"/>
-      <c r="BU40" s="167"/>
-      <c r="BV40" s="168"/>
-      <c r="BW40" s="157"/>
-      <c r="BX40" s="158"/>
-      <c r="BY40" s="158"/>
-      <c r="BZ40" s="159"/>
+      <c r="BP40" s="124"/>
+      <c r="BQ40" s="125"/>
+      <c r="BR40" s="126"/>
+      <c r="BS40" s="133"/>
+      <c r="BT40" s="134"/>
+      <c r="BU40" s="134"/>
+      <c r="BV40" s="135"/>
+      <c r="BW40" s="124"/>
+      <c r="BX40" s="125"/>
+      <c r="BY40" s="125"/>
+      <c r="BZ40" s="126"/>
     </row>
     <row r="41" spans="1:78" ht="18.75" customHeight="1">
       <c r="A41" s="25"/>
@@ -9375,17 +9346,17 @@
       <c r="BM41" s="30"/>
       <c r="BN41" s="26"/>
       <c r="BO41" s="26"/>
-      <c r="BP41" s="160"/>
-      <c r="BQ41" s="161"/>
-      <c r="BR41" s="162"/>
-      <c r="BS41" s="169"/>
-      <c r="BT41" s="170"/>
-      <c r="BU41" s="170"/>
-      <c r="BV41" s="171"/>
-      <c r="BW41" s="160"/>
-      <c r="BX41" s="161"/>
-      <c r="BY41" s="161"/>
-      <c r="BZ41" s="162"/>
+      <c r="BP41" s="127"/>
+      <c r="BQ41" s="128"/>
+      <c r="BR41" s="129"/>
+      <c r="BS41" s="136"/>
+      <c r="BT41" s="137"/>
+      <c r="BU41" s="137"/>
+      <c r="BV41" s="138"/>
+      <c r="BW41" s="127"/>
+      <c r="BX41" s="128"/>
+      <c r="BY41" s="128"/>
+      <c r="BZ41" s="129"/>
     </row>
     <row r="42" spans="1:78" ht="18.75" customHeight="1">
       <c r="A42" s="4" t="s">
@@ -9473,23 +9444,23 @@
       <c r="BM42" s="11"/>
       <c r="BN42" s="5"/>
       <c r="BO42" s="5"/>
-      <c r="BP42" s="154" t="s">
+      <c r="BP42" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ42" s="155"/>
-      <c r="BR42" s="156"/>
-      <c r="BS42" s="163">
+      <c r="BQ42" s="122"/>
+      <c r="BR42" s="123"/>
+      <c r="BS42" s="130">
         <v>45583</v>
       </c>
-      <c r="BT42" s="164"/>
-      <c r="BU42" s="164"/>
-      <c r="BV42" s="165"/>
-      <c r="BW42" s="154" t="s">
+      <c r="BT42" s="131"/>
+      <c r="BU42" s="131"/>
+      <c r="BV42" s="132"/>
+      <c r="BW42" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX42" s="155"/>
-      <c r="BY42" s="155"/>
-      <c r="BZ42" s="156"/>
+      <c r="BX42" s="122"/>
+      <c r="BY42" s="122"/>
+      <c r="BZ42" s="123"/>
     </row>
     <row r="43" spans="1:78" ht="18.75" customHeight="1">
       <c r="A43" s="14"/>
@@ -9565,17 +9536,17 @@
       <c r="BM43" s="21"/>
       <c r="BN43" s="15"/>
       <c r="BO43" s="15"/>
-      <c r="BP43" s="157"/>
-      <c r="BQ43" s="158"/>
-      <c r="BR43" s="159"/>
-      <c r="BS43" s="166"/>
-      <c r="BT43" s="167"/>
-      <c r="BU43" s="167"/>
-      <c r="BV43" s="168"/>
-      <c r="BW43" s="157"/>
-      <c r="BX43" s="158"/>
-      <c r="BY43" s="158"/>
-      <c r="BZ43" s="159"/>
+      <c r="BP43" s="124"/>
+      <c r="BQ43" s="125"/>
+      <c r="BR43" s="126"/>
+      <c r="BS43" s="133"/>
+      <c r="BT43" s="134"/>
+      <c r="BU43" s="134"/>
+      <c r="BV43" s="135"/>
+      <c r="BW43" s="124"/>
+      <c r="BX43" s="125"/>
+      <c r="BY43" s="125"/>
+      <c r="BZ43" s="126"/>
     </row>
     <row r="44" spans="1:78" ht="18.75" customHeight="1">
       <c r="A44" s="14"/>
@@ -9647,17 +9618,17 @@
       <c r="BM44" s="21"/>
       <c r="BN44" s="15"/>
       <c r="BO44" s="15"/>
-      <c r="BP44" s="157"/>
-      <c r="BQ44" s="158"/>
-      <c r="BR44" s="159"/>
-      <c r="BS44" s="166"/>
-      <c r="BT44" s="167"/>
-      <c r="BU44" s="167"/>
-      <c r="BV44" s="168"/>
-      <c r="BW44" s="157"/>
-      <c r="BX44" s="158"/>
-      <c r="BY44" s="158"/>
-      <c r="BZ44" s="159"/>
+      <c r="BP44" s="124"/>
+      <c r="BQ44" s="125"/>
+      <c r="BR44" s="126"/>
+      <c r="BS44" s="133"/>
+      <c r="BT44" s="134"/>
+      <c r="BU44" s="134"/>
+      <c r="BV44" s="135"/>
+      <c r="BW44" s="124"/>
+      <c r="BX44" s="125"/>
+      <c r="BY44" s="125"/>
+      <c r="BZ44" s="126"/>
     </row>
     <row r="45" spans="1:78" ht="18.75" customHeight="1">
       <c r="A45" s="25"/>
@@ -9729,17 +9700,17 @@
       <c r="BM45" s="30"/>
       <c r="BN45" s="26"/>
       <c r="BO45" s="26"/>
-      <c r="BP45" s="160"/>
-      <c r="BQ45" s="161"/>
-      <c r="BR45" s="162"/>
-      <c r="BS45" s="169"/>
-      <c r="BT45" s="170"/>
-      <c r="BU45" s="170"/>
-      <c r="BV45" s="171"/>
-      <c r="BW45" s="160"/>
-      <c r="BX45" s="161"/>
-      <c r="BY45" s="161"/>
-      <c r="BZ45" s="162"/>
+      <c r="BP45" s="127"/>
+      <c r="BQ45" s="128"/>
+      <c r="BR45" s="129"/>
+      <c r="BS45" s="136"/>
+      <c r="BT45" s="137"/>
+      <c r="BU45" s="137"/>
+      <c r="BV45" s="138"/>
+      <c r="BW45" s="127"/>
+      <c r="BX45" s="128"/>
+      <c r="BY45" s="128"/>
+      <c r="BZ45" s="129"/>
     </row>
     <row r="46" spans="1:78" ht="18.75" customHeight="1">
       <c r="A46" s="32" t="s">
@@ -9827,23 +9798,23 @@
       <c r="BM46" s="21"/>
       <c r="BN46" s="15"/>
       <c r="BO46" s="15"/>
-      <c r="BP46" s="154" t="s">
+      <c r="BP46" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ46" s="155"/>
-      <c r="BR46" s="156"/>
-      <c r="BS46" s="163">
+      <c r="BQ46" s="122"/>
+      <c r="BR46" s="123"/>
+      <c r="BS46" s="130">
         <v>45583</v>
       </c>
-      <c r="BT46" s="164"/>
-      <c r="BU46" s="164"/>
-      <c r="BV46" s="165"/>
-      <c r="BW46" s="154" t="s">
+      <c r="BT46" s="131"/>
+      <c r="BU46" s="131"/>
+      <c r="BV46" s="132"/>
+      <c r="BW46" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX46" s="155"/>
-      <c r="BY46" s="155"/>
-      <c r="BZ46" s="156"/>
+      <c r="BX46" s="122"/>
+      <c r="BY46" s="122"/>
+      <c r="BZ46" s="123"/>
     </row>
     <row r="47" spans="1:78" ht="18.75" customHeight="1">
       <c r="A47" s="32"/>
@@ -9919,17 +9890,17 @@
       <c r="BM47" s="21"/>
       <c r="BN47" s="15"/>
       <c r="BO47" s="15"/>
-      <c r="BP47" s="157"/>
-      <c r="BQ47" s="158"/>
-      <c r="BR47" s="159"/>
-      <c r="BS47" s="166"/>
-      <c r="BT47" s="167"/>
-      <c r="BU47" s="167"/>
-      <c r="BV47" s="168"/>
-      <c r="BW47" s="157"/>
-      <c r="BX47" s="158"/>
-      <c r="BY47" s="158"/>
-      <c r="BZ47" s="159"/>
+      <c r="BP47" s="124"/>
+      <c r="BQ47" s="125"/>
+      <c r="BR47" s="126"/>
+      <c r="BS47" s="133"/>
+      <c r="BT47" s="134"/>
+      <c r="BU47" s="134"/>
+      <c r="BV47" s="135"/>
+      <c r="BW47" s="124"/>
+      <c r="BX47" s="125"/>
+      <c r="BY47" s="125"/>
+      <c r="BZ47" s="126"/>
     </row>
     <row r="48" spans="1:78" ht="18.75" customHeight="1">
       <c r="A48" s="32"/>
@@ -10001,17 +9972,17 @@
       <c r="BM48" s="21"/>
       <c r="BN48" s="15"/>
       <c r="BO48" s="15"/>
-      <c r="BP48" s="157"/>
-      <c r="BQ48" s="158"/>
-      <c r="BR48" s="159"/>
-      <c r="BS48" s="166"/>
-      <c r="BT48" s="167"/>
-      <c r="BU48" s="167"/>
-      <c r="BV48" s="168"/>
-      <c r="BW48" s="157"/>
-      <c r="BX48" s="158"/>
-      <c r="BY48" s="158"/>
-      <c r="BZ48" s="159"/>
+      <c r="BP48" s="124"/>
+      <c r="BQ48" s="125"/>
+      <c r="BR48" s="126"/>
+      <c r="BS48" s="133"/>
+      <c r="BT48" s="134"/>
+      <c r="BU48" s="134"/>
+      <c r="BV48" s="135"/>
+      <c r="BW48" s="124"/>
+      <c r="BX48" s="125"/>
+      <c r="BY48" s="125"/>
+      <c r="BZ48" s="126"/>
     </row>
     <row r="49" spans="1:78" ht="18.75" customHeight="1">
       <c r="A49" s="33"/>
@@ -10083,17 +10054,17 @@
       <c r="BM49" s="30"/>
       <c r="BN49" s="26"/>
       <c r="BO49" s="26"/>
-      <c r="BP49" s="160"/>
-      <c r="BQ49" s="161"/>
-      <c r="BR49" s="162"/>
-      <c r="BS49" s="169"/>
-      <c r="BT49" s="170"/>
-      <c r="BU49" s="170"/>
-      <c r="BV49" s="171"/>
-      <c r="BW49" s="160"/>
-      <c r="BX49" s="161"/>
-      <c r="BY49" s="161"/>
-      <c r="BZ49" s="162"/>
+      <c r="BP49" s="127"/>
+      <c r="BQ49" s="128"/>
+      <c r="BR49" s="129"/>
+      <c r="BS49" s="136"/>
+      <c r="BT49" s="137"/>
+      <c r="BU49" s="137"/>
+      <c r="BV49" s="138"/>
+      <c r="BW49" s="127"/>
+      <c r="BX49" s="128"/>
+      <c r="BY49" s="128"/>
+      <c r="BZ49" s="129"/>
     </row>
     <row r="50" spans="1:78" ht="18.75" customHeight="1">
       <c r="A50" s="32" t="s">
@@ -10181,23 +10152,23 @@
       <c r="BM50" s="21"/>
       <c r="BN50" s="15"/>
       <c r="BO50" s="15"/>
-      <c r="BP50" s="154" t="s">
+      <c r="BP50" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ50" s="155"/>
-      <c r="BR50" s="156"/>
-      <c r="BS50" s="163">
+      <c r="BQ50" s="122"/>
+      <c r="BR50" s="123"/>
+      <c r="BS50" s="130">
         <v>45583</v>
       </c>
-      <c r="BT50" s="164"/>
-      <c r="BU50" s="164"/>
-      <c r="BV50" s="165"/>
-      <c r="BW50" s="154" t="s">
+      <c r="BT50" s="131"/>
+      <c r="BU50" s="131"/>
+      <c r="BV50" s="132"/>
+      <c r="BW50" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX50" s="155"/>
-      <c r="BY50" s="155"/>
-      <c r="BZ50" s="156"/>
+      <c r="BX50" s="122"/>
+      <c r="BY50" s="122"/>
+      <c r="BZ50" s="123"/>
     </row>
     <row r="51" spans="1:78" ht="18.75" customHeight="1">
       <c r="A51" s="32"/>
@@ -10273,17 +10244,17 @@
       <c r="BM51" s="21"/>
       <c r="BN51" s="15"/>
       <c r="BO51" s="15"/>
-      <c r="BP51" s="157"/>
-      <c r="BQ51" s="158"/>
-      <c r="BR51" s="159"/>
-      <c r="BS51" s="166"/>
-      <c r="BT51" s="167"/>
-      <c r="BU51" s="167"/>
-      <c r="BV51" s="168"/>
-      <c r="BW51" s="157"/>
-      <c r="BX51" s="158"/>
-      <c r="BY51" s="158"/>
-      <c r="BZ51" s="159"/>
+      <c r="BP51" s="124"/>
+      <c r="BQ51" s="125"/>
+      <c r="BR51" s="126"/>
+      <c r="BS51" s="133"/>
+      <c r="BT51" s="134"/>
+      <c r="BU51" s="134"/>
+      <c r="BV51" s="135"/>
+      <c r="BW51" s="124"/>
+      <c r="BX51" s="125"/>
+      <c r="BY51" s="125"/>
+      <c r="BZ51" s="126"/>
     </row>
     <row r="52" spans="1:78" ht="18.75" customHeight="1">
       <c r="A52" s="32"/>
@@ -10355,17 +10326,17 @@
       <c r="BM52" s="21"/>
       <c r="BN52" s="15"/>
       <c r="BO52" s="15"/>
-      <c r="BP52" s="157"/>
-      <c r="BQ52" s="158"/>
-      <c r="BR52" s="159"/>
-      <c r="BS52" s="166"/>
-      <c r="BT52" s="167"/>
-      <c r="BU52" s="167"/>
-      <c r="BV52" s="168"/>
-      <c r="BW52" s="157"/>
-      <c r="BX52" s="158"/>
-      <c r="BY52" s="158"/>
-      <c r="BZ52" s="159"/>
+      <c r="BP52" s="124"/>
+      <c r="BQ52" s="125"/>
+      <c r="BR52" s="126"/>
+      <c r="BS52" s="133"/>
+      <c r="BT52" s="134"/>
+      <c r="BU52" s="134"/>
+      <c r="BV52" s="135"/>
+      <c r="BW52" s="124"/>
+      <c r="BX52" s="125"/>
+      <c r="BY52" s="125"/>
+      <c r="BZ52" s="126"/>
     </row>
     <row r="53" spans="1:78" ht="18.75" customHeight="1">
       <c r="A53" s="33"/>
@@ -10437,17 +10408,17 @@
       <c r="BM53" s="30"/>
       <c r="BN53" s="26"/>
       <c r="BO53" s="26"/>
-      <c r="BP53" s="160"/>
-      <c r="BQ53" s="161"/>
-      <c r="BR53" s="162"/>
-      <c r="BS53" s="169"/>
-      <c r="BT53" s="170"/>
-      <c r="BU53" s="170"/>
-      <c r="BV53" s="171"/>
-      <c r="BW53" s="160"/>
-      <c r="BX53" s="161"/>
-      <c r="BY53" s="161"/>
-      <c r="BZ53" s="162"/>
+      <c r="BP53" s="127"/>
+      <c r="BQ53" s="128"/>
+      <c r="BR53" s="129"/>
+      <c r="BS53" s="136"/>
+      <c r="BT53" s="137"/>
+      <c r="BU53" s="137"/>
+      <c r="BV53" s="138"/>
+      <c r="BW53" s="127"/>
+      <c r="BX53" s="128"/>
+      <c r="BY53" s="128"/>
+      <c r="BZ53" s="129"/>
     </row>
     <row r="54" spans="1:78" ht="18.75" customHeight="1">
       <c r="A54" s="32" t="s">
@@ -10535,23 +10506,23 @@
       <c r="BM54" s="21"/>
       <c r="BN54" s="15"/>
       <c r="BO54" s="15"/>
-      <c r="BP54" s="154" t="s">
+      <c r="BP54" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ54" s="155"/>
-      <c r="BR54" s="156"/>
-      <c r="BS54" s="163">
+      <c r="BQ54" s="122"/>
+      <c r="BR54" s="123"/>
+      <c r="BS54" s="130">
         <v>45583</v>
       </c>
-      <c r="BT54" s="164"/>
-      <c r="BU54" s="164"/>
-      <c r="BV54" s="165"/>
-      <c r="BW54" s="154" t="s">
+      <c r="BT54" s="131"/>
+      <c r="BU54" s="131"/>
+      <c r="BV54" s="132"/>
+      <c r="BW54" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX54" s="155"/>
-      <c r="BY54" s="155"/>
-      <c r="BZ54" s="156"/>
+      <c r="BX54" s="122"/>
+      <c r="BY54" s="122"/>
+      <c r="BZ54" s="123"/>
     </row>
     <row r="55" spans="1:78" ht="18.75" customHeight="1">
       <c r="A55" s="32"/>
@@ -10627,17 +10598,17 @@
       <c r="BM55" s="21"/>
       <c r="BN55" s="15"/>
       <c r="BO55" s="15"/>
-      <c r="BP55" s="157"/>
-      <c r="BQ55" s="158"/>
-      <c r="BR55" s="159"/>
-      <c r="BS55" s="166"/>
-      <c r="BT55" s="167"/>
-      <c r="BU55" s="167"/>
-      <c r="BV55" s="168"/>
-      <c r="BW55" s="157"/>
-      <c r="BX55" s="158"/>
-      <c r="BY55" s="158"/>
-      <c r="BZ55" s="159"/>
+      <c r="BP55" s="124"/>
+      <c r="BQ55" s="125"/>
+      <c r="BR55" s="126"/>
+      <c r="BS55" s="133"/>
+      <c r="BT55" s="134"/>
+      <c r="BU55" s="134"/>
+      <c r="BV55" s="135"/>
+      <c r="BW55" s="124"/>
+      <c r="BX55" s="125"/>
+      <c r="BY55" s="125"/>
+      <c r="BZ55" s="126"/>
     </row>
     <row r="56" spans="1:78" ht="18.75" customHeight="1">
       <c r="A56" s="32"/>
@@ -10709,17 +10680,17 @@
       <c r="BM56" s="21"/>
       <c r="BN56" s="15"/>
       <c r="BO56" s="15"/>
-      <c r="BP56" s="157"/>
-      <c r="BQ56" s="158"/>
-      <c r="BR56" s="159"/>
-      <c r="BS56" s="166"/>
-      <c r="BT56" s="167"/>
-      <c r="BU56" s="167"/>
-      <c r="BV56" s="168"/>
-      <c r="BW56" s="157"/>
-      <c r="BX56" s="158"/>
-      <c r="BY56" s="158"/>
-      <c r="BZ56" s="159"/>
+      <c r="BP56" s="124"/>
+      <c r="BQ56" s="125"/>
+      <c r="BR56" s="126"/>
+      <c r="BS56" s="133"/>
+      <c r="BT56" s="134"/>
+      <c r="BU56" s="134"/>
+      <c r="BV56" s="135"/>
+      <c r="BW56" s="124"/>
+      <c r="BX56" s="125"/>
+      <c r="BY56" s="125"/>
+      <c r="BZ56" s="126"/>
     </row>
     <row r="57" spans="1:78" ht="18.75" customHeight="1">
       <c r="A57" s="34"/>
@@ -10791,17 +10762,17 @@
       <c r="BM57" s="30"/>
       <c r="BN57" s="26"/>
       <c r="BO57" s="26"/>
-      <c r="BP57" s="160"/>
-      <c r="BQ57" s="161"/>
-      <c r="BR57" s="162"/>
-      <c r="BS57" s="169"/>
-      <c r="BT57" s="170"/>
-      <c r="BU57" s="170"/>
-      <c r="BV57" s="171"/>
-      <c r="BW57" s="160"/>
-      <c r="BX57" s="161"/>
-      <c r="BY57" s="161"/>
-      <c r="BZ57" s="162"/>
+      <c r="BP57" s="127"/>
+      <c r="BQ57" s="128"/>
+      <c r="BR57" s="129"/>
+      <c r="BS57" s="136"/>
+      <c r="BT57" s="137"/>
+      <c r="BU57" s="137"/>
+      <c r="BV57" s="138"/>
+      <c r="BW57" s="127"/>
+      <c r="BX57" s="128"/>
+      <c r="BY57" s="128"/>
+      <c r="BZ57" s="129"/>
     </row>
     <row r="58" spans="1:78" s="19" customFormat="1" ht="18.75" customHeight="1">
       <c r="A58" s="12">
@@ -10889,23 +10860,23 @@
       <c r="BM58" s="9"/>
       <c r="BN58" s="9"/>
       <c r="BO58" s="23"/>
-      <c r="BP58" s="154" t="s">
+      <c r="BP58" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ58" s="155"/>
-      <c r="BR58" s="156"/>
-      <c r="BS58" s="163">
+      <c r="BQ58" s="122"/>
+      <c r="BR58" s="123"/>
+      <c r="BS58" s="130">
         <v>45583</v>
       </c>
-      <c r="BT58" s="164"/>
-      <c r="BU58" s="164"/>
-      <c r="BV58" s="165"/>
-      <c r="BW58" s="154" t="s">
+      <c r="BT58" s="131"/>
+      <c r="BU58" s="131"/>
+      <c r="BV58" s="132"/>
+      <c r="BW58" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX58" s="155"/>
-      <c r="BY58" s="155"/>
-      <c r="BZ58" s="156"/>
+      <c r="BX58" s="122"/>
+      <c r="BY58" s="122"/>
+      <c r="BZ58" s="123"/>
     </row>
     <row r="59" spans="1:78" s="19" customFormat="1" ht="18.75" customHeight="1">
       <c r="A59" s="18"/>
@@ -10981,17 +10952,17 @@
       <c r="BM59" s="73"/>
       <c r="BN59" s="73"/>
       <c r="BO59" s="24"/>
-      <c r="BP59" s="157"/>
-      <c r="BQ59" s="158"/>
-      <c r="BR59" s="159"/>
-      <c r="BS59" s="166"/>
-      <c r="BT59" s="167"/>
-      <c r="BU59" s="167"/>
-      <c r="BV59" s="168"/>
-      <c r="BW59" s="157"/>
-      <c r="BX59" s="158"/>
-      <c r="BY59" s="158"/>
-      <c r="BZ59" s="159"/>
+      <c r="BP59" s="124"/>
+      <c r="BQ59" s="125"/>
+      <c r="BR59" s="126"/>
+      <c r="BS59" s="133"/>
+      <c r="BT59" s="134"/>
+      <c r="BU59" s="134"/>
+      <c r="BV59" s="135"/>
+      <c r="BW59" s="124"/>
+      <c r="BX59" s="125"/>
+      <c r="BY59" s="125"/>
+      <c r="BZ59" s="126"/>
     </row>
     <row r="60" spans="1:78" s="19" customFormat="1" ht="18.75" customHeight="1">
       <c r="A60" s="39"/>
@@ -11065,17 +11036,17 @@
       <c r="BM60" s="74"/>
       <c r="BN60" s="74"/>
       <c r="BO60" s="40"/>
-      <c r="BP60" s="160"/>
-      <c r="BQ60" s="161"/>
-      <c r="BR60" s="162"/>
-      <c r="BS60" s="169"/>
-      <c r="BT60" s="170"/>
-      <c r="BU60" s="170"/>
-      <c r="BV60" s="171"/>
-      <c r="BW60" s="160"/>
-      <c r="BX60" s="161"/>
-      <c r="BY60" s="161"/>
-      <c r="BZ60" s="162"/>
+      <c r="BP60" s="127"/>
+      <c r="BQ60" s="128"/>
+      <c r="BR60" s="129"/>
+      <c r="BS60" s="136"/>
+      <c r="BT60" s="137"/>
+      <c r="BU60" s="137"/>
+      <c r="BV60" s="138"/>
+      <c r="BW60" s="127"/>
+      <c r="BX60" s="128"/>
+      <c r="BY60" s="128"/>
+      <c r="BZ60" s="129"/>
     </row>
     <row r="61" spans="1:78" s="19" customFormat="1" ht="18.75" customHeight="1">
       <c r="A61" s="12">
@@ -11163,23 +11134,23 @@
       <c r="BM61" s="9"/>
       <c r="BN61" s="9"/>
       <c r="BO61" s="23"/>
-      <c r="BP61" s="154" t="s">
+      <c r="BP61" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="BQ61" s="155"/>
-      <c r="BR61" s="156"/>
-      <c r="BS61" s="163">
+      <c r="BQ61" s="122"/>
+      <c r="BR61" s="123"/>
+      <c r="BS61" s="130">
         <v>45583</v>
       </c>
-      <c r="BT61" s="164"/>
-      <c r="BU61" s="164"/>
-      <c r="BV61" s="165"/>
-      <c r="BW61" s="154" t="s">
+      <c r="BT61" s="131"/>
+      <c r="BU61" s="131"/>
+      <c r="BV61" s="132"/>
+      <c r="BW61" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="BX61" s="155"/>
-      <c r="BY61" s="155"/>
-      <c r="BZ61" s="156"/>
+      <c r="BX61" s="122"/>
+      <c r="BY61" s="122"/>
+      <c r="BZ61" s="123"/>
     </row>
     <row r="62" spans="1:78" s="19" customFormat="1" ht="18.75" customHeight="1">
       <c r="A62" s="18"/>
@@ -11255,17 +11226,17 @@
       <c r="BM62" s="73"/>
       <c r="BN62" s="73"/>
       <c r="BO62" s="24"/>
-      <c r="BP62" s="157"/>
-      <c r="BQ62" s="158"/>
-      <c r="BR62" s="159"/>
-      <c r="BS62" s="166"/>
-      <c r="BT62" s="167"/>
-      <c r="BU62" s="167"/>
-      <c r="BV62" s="168"/>
-      <c r="BW62" s="157"/>
-      <c r="BX62" s="158"/>
-      <c r="BY62" s="158"/>
-      <c r="BZ62" s="159"/>
+      <c r="BP62" s="124"/>
+      <c r="BQ62" s="125"/>
+      <c r="BR62" s="126"/>
+      <c r="BS62" s="133"/>
+      <c r="BT62" s="134"/>
+      <c r="BU62" s="134"/>
+      <c r="BV62" s="135"/>
+      <c r="BW62" s="124"/>
+      <c r="BX62" s="125"/>
+      <c r="BY62" s="125"/>
+      <c r="BZ62" s="126"/>
     </row>
     <row r="63" spans="1:78" s="19" customFormat="1" ht="18.75" customHeight="1">
       <c r="A63" s="39"/>
@@ -11337,20 +11308,73 @@
       <c r="BM63" s="74"/>
       <c r="BN63" s="74"/>
       <c r="BO63" s="40"/>
-      <c r="BP63" s="160"/>
-      <c r="BQ63" s="161"/>
-      <c r="BR63" s="162"/>
-      <c r="BS63" s="169"/>
-      <c r="BT63" s="170"/>
-      <c r="BU63" s="170"/>
-      <c r="BV63" s="171"/>
-      <c r="BW63" s="160"/>
-      <c r="BX63" s="161"/>
-      <c r="BY63" s="161"/>
-      <c r="BZ63" s="162"/>
+      <c r="BP63" s="127"/>
+      <c r="BQ63" s="128"/>
+      <c r="BR63" s="129"/>
+      <c r="BS63" s="136"/>
+      <c r="BT63" s="137"/>
+      <c r="BU63" s="137"/>
+      <c r="BV63" s="138"/>
+      <c r="BW63" s="127"/>
+      <c r="BX63" s="128"/>
+      <c r="BY63" s="128"/>
+      <c r="BZ63" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="BP61:BR63"/>
+    <mergeCell ref="BS61:BV63"/>
+    <mergeCell ref="BW61:BZ63"/>
+    <mergeCell ref="BP50:BR53"/>
+    <mergeCell ref="BS50:BV53"/>
+    <mergeCell ref="BW50:BZ53"/>
+    <mergeCell ref="BP54:BR57"/>
+    <mergeCell ref="BS54:BV57"/>
+    <mergeCell ref="BW54:BZ57"/>
+    <mergeCell ref="BP58:BR60"/>
+    <mergeCell ref="BS58:BV60"/>
+    <mergeCell ref="BW58:BZ60"/>
+    <mergeCell ref="BP42:BR45"/>
+    <mergeCell ref="BS42:BV45"/>
+    <mergeCell ref="BW42:BZ45"/>
+    <mergeCell ref="BP30:BR33"/>
+    <mergeCell ref="BS30:BV33"/>
+    <mergeCell ref="BW30:BZ33"/>
+    <mergeCell ref="BP34:BR37"/>
+    <mergeCell ref="BS34:BV37"/>
+    <mergeCell ref="BW34:BZ37"/>
+    <mergeCell ref="BP38:BR41"/>
+    <mergeCell ref="BS38:BV41"/>
+    <mergeCell ref="BW38:BZ41"/>
+    <mergeCell ref="BP22:BR25"/>
+    <mergeCell ref="BS22:BV25"/>
+    <mergeCell ref="BW22:BZ25"/>
+    <mergeCell ref="BP26:BR29"/>
+    <mergeCell ref="BS26:BV29"/>
+    <mergeCell ref="BW26:BZ29"/>
+    <mergeCell ref="BP14:BR17"/>
+    <mergeCell ref="BS14:BV17"/>
+    <mergeCell ref="BW14:BZ17"/>
+    <mergeCell ref="BP18:BR21"/>
+    <mergeCell ref="BS18:BV21"/>
+    <mergeCell ref="BW18:BZ21"/>
+    <mergeCell ref="BP7:BR9"/>
+    <mergeCell ref="BS7:BV9"/>
+    <mergeCell ref="BW7:BZ9"/>
+    <mergeCell ref="BP10:BR13"/>
+    <mergeCell ref="BS10:BV13"/>
+    <mergeCell ref="BW10:BZ13"/>
+    <mergeCell ref="AO1:AR1"/>
+    <mergeCell ref="AS1:BB1"/>
+    <mergeCell ref="BC1:BD2"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:I6"/>
+    <mergeCell ref="J5:X5"/>
+    <mergeCell ref="Y5:AE6"/>
+    <mergeCell ref="AF5:AS6"/>
+    <mergeCell ref="J6:N6"/>
+    <mergeCell ref="O6:T6"/>
+    <mergeCell ref="U6:X6"/>
     <mergeCell ref="BP46:BR49"/>
     <mergeCell ref="BS46:BV49"/>
     <mergeCell ref="BW46:BZ49"/>
@@ -11367,59 +11391,6 @@
     <mergeCell ref="AS2:BB2"/>
     <mergeCell ref="V1:AD1"/>
     <mergeCell ref="AE1:AN1"/>
-    <mergeCell ref="AO1:AR1"/>
-    <mergeCell ref="AS1:BB1"/>
-    <mergeCell ref="BC1:BD2"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:I6"/>
-    <mergeCell ref="J5:X5"/>
-    <mergeCell ref="Y5:AE6"/>
-    <mergeCell ref="AF5:AS6"/>
-    <mergeCell ref="J6:N6"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="U6:X6"/>
-    <mergeCell ref="BP7:BR9"/>
-    <mergeCell ref="BS7:BV9"/>
-    <mergeCell ref="BW7:BZ9"/>
-    <mergeCell ref="BP10:BR13"/>
-    <mergeCell ref="BS10:BV13"/>
-    <mergeCell ref="BW10:BZ13"/>
-    <mergeCell ref="BP14:BR17"/>
-    <mergeCell ref="BS14:BV17"/>
-    <mergeCell ref="BW14:BZ17"/>
-    <mergeCell ref="BP18:BR21"/>
-    <mergeCell ref="BS18:BV21"/>
-    <mergeCell ref="BW18:BZ21"/>
-    <mergeCell ref="BP22:BR25"/>
-    <mergeCell ref="BS22:BV25"/>
-    <mergeCell ref="BW22:BZ25"/>
-    <mergeCell ref="BP26:BR29"/>
-    <mergeCell ref="BS26:BV29"/>
-    <mergeCell ref="BW26:BZ29"/>
-    <mergeCell ref="BP42:BR45"/>
-    <mergeCell ref="BS42:BV45"/>
-    <mergeCell ref="BW42:BZ45"/>
-    <mergeCell ref="BP30:BR33"/>
-    <mergeCell ref="BS30:BV33"/>
-    <mergeCell ref="BW30:BZ33"/>
-    <mergeCell ref="BP34:BR37"/>
-    <mergeCell ref="BS34:BV37"/>
-    <mergeCell ref="BW34:BZ37"/>
-    <mergeCell ref="BP38:BR41"/>
-    <mergeCell ref="BS38:BV41"/>
-    <mergeCell ref="BW38:BZ41"/>
-    <mergeCell ref="BP61:BR63"/>
-    <mergeCell ref="BS61:BV63"/>
-    <mergeCell ref="BW61:BZ63"/>
-    <mergeCell ref="BP50:BR53"/>
-    <mergeCell ref="BS50:BV53"/>
-    <mergeCell ref="BW50:BZ53"/>
-    <mergeCell ref="BP54:BR57"/>
-    <mergeCell ref="BS54:BV57"/>
-    <mergeCell ref="BW54:BZ57"/>
-    <mergeCell ref="BP58:BR60"/>
-    <mergeCell ref="BS58:BV60"/>
-    <mergeCell ref="BW58:BZ60"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.39370078740157483" footer="0.39370078740157483"/>
@@ -11445,60 +11416,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="13.9" customHeight="1" thickTop="1">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="115" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="204" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="205"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="208"/>
-      <c r="I1" s="204" t="s">
+      <c r="E1" s="164"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="205"/>
-      <c r="K1" s="209">
+      <c r="J1" s="164"/>
+      <c r="K1" s="108">
         <v>45567</v>
       </c>
-      <c r="L1" s="210"/>
+      <c r="L1" s="110"/>
       <c r="M1" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="N1" s="202" t="s">
+      <c r="N1" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="195"/>
+      <c r="O1" s="168"/>
     </row>
     <row r="2" spans="1:15" ht="13.9" customHeight="1" thickBot="1">
-      <c r="A2" s="136"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="197" t="s">
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="170" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="198"/>
-      <c r="F2" s="144" t="s">
+      <c r="E2" s="171"/>
+      <c r="F2" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="145"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="197" t="s">
+      <c r="G2" s="105"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="170" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="198"/>
-      <c r="K2" s="200" t="s">
+      <c r="J2" s="171"/>
+      <c r="K2" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="201"/>
+      <c r="L2" s="113"/>
       <c r="M2" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="203"/>
-      <c r="O2" s="196"/>
+      <c r="N2" s="174"/>
+      <c r="O2" s="169"/>
     </row>
     <row r="3" spans="1:15" ht="14.25" thickTop="1">
       <c r="A3" s="41" t="s">
@@ -12048,17 +12019,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N1:N2"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12081,60 +12052,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="14.25" thickTop="1">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="115" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="204" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="205"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="208"/>
-      <c r="I1" s="204" t="s">
+      <c r="E1" s="164"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="205"/>
-      <c r="K1" s="209">
+      <c r="J1" s="164"/>
+      <c r="K1" s="108">
         <v>45567</v>
       </c>
-      <c r="L1" s="210"/>
+      <c r="L1" s="110"/>
       <c r="M1" s="60">
         <v>45576</v>
       </c>
-      <c r="N1" s="202" t="s">
+      <c r="N1" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="195"/>
+      <c r="O1" s="168"/>
     </row>
     <row r="2" spans="1:15" ht="14.25" thickBot="1">
-      <c r="A2" s="136"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="197" t="s">
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="170" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="198"/>
-      <c r="F2" s="144" t="s">
+      <c r="E2" s="171"/>
+      <c r="F2" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="145"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="197" t="s">
+      <c r="G2" s="105"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="170" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="198"/>
-      <c r="K2" s="200" t="s">
+      <c r="J2" s="171"/>
+      <c r="K2" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="201"/>
+      <c r="L2" s="113"/>
       <c r="M2" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="203"/>
-      <c r="O2" s="196"/>
+      <c r="N2" s="174"/>
+      <c r="O2" s="169"/>
     </row>
     <row r="3" spans="1:15" ht="14.25" thickTop="1">
       <c r="A3" s="41" t="s">
@@ -12450,17 +12421,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N1:N2"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12482,60 +12453,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="14.25" thickTop="1">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="115" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="204" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="205"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="208"/>
-      <c r="I1" s="204" t="s">
+      <c r="E1" s="164"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="205"/>
-      <c r="K1" s="209">
+      <c r="J1" s="164"/>
+      <c r="K1" s="108">
         <v>45567</v>
       </c>
-      <c r="L1" s="210"/>
+      <c r="L1" s="110"/>
       <c r="M1" s="60">
         <v>45576</v>
       </c>
-      <c r="N1" s="202" t="s">
+      <c r="N1" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="195"/>
+      <c r="O1" s="168"/>
     </row>
     <row r="2" spans="1:15" ht="14.25" thickBot="1">
-      <c r="A2" s="136"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="197" t="s">
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="170" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="198"/>
-      <c r="F2" s="144" t="s">
+      <c r="E2" s="171"/>
+      <c r="F2" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="145"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="197" t="s">
+      <c r="G2" s="105"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="170" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="198"/>
-      <c r="K2" s="200" t="s">
+      <c r="J2" s="171"/>
+      <c r="K2" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="201"/>
+      <c r="L2" s="113"/>
       <c r="M2" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="203"/>
-      <c r="O2" s="196"/>
+      <c r="N2" s="174"/>
+      <c r="O2" s="169"/>
     </row>
     <row r="3" spans="1:15" ht="14.25" thickTop="1">
       <c r="A3" s="41" t="s">
@@ -12799,17 +12770,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N1:N2"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12831,60 +12802,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="13.9" customHeight="1" thickTop="1">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="115" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="204" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="205"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="208"/>
-      <c r="I1" s="204" t="s">
+      <c r="E1" s="164"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="205"/>
-      <c r="K1" s="209">
+      <c r="J1" s="164"/>
+      <c r="K1" s="108">
         <v>45567</v>
       </c>
-      <c r="L1" s="210"/>
+      <c r="L1" s="110"/>
       <c r="M1" s="60">
         <v>45576</v>
       </c>
-      <c r="N1" s="202" t="s">
+      <c r="N1" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="195"/>
+      <c r="O1" s="168"/>
     </row>
     <row r="2" spans="1:15" ht="13.9" customHeight="1" thickBot="1">
-      <c r="A2" s="136"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="197" t="s">
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="170" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="198"/>
-      <c r="F2" s="144" t="s">
+      <c r="E2" s="171"/>
+      <c r="F2" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="145"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="197" t="s">
+      <c r="G2" s="105"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="170" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="198"/>
-      <c r="K2" s="200" t="s">
+      <c r="J2" s="171"/>
+      <c r="K2" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="201"/>
+      <c r="L2" s="113"/>
       <c r="M2" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="203"/>
-      <c r="O2" s="196"/>
+      <c r="N2" s="174"/>
+      <c r="O2" s="169"/>
     </row>
     <row r="3" spans="1:15" ht="13.9" customHeight="1" thickTop="1">
       <c r="A3" s="57" t="s">
@@ -12907,17 +12878,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N1:N2"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13629,5 +13600,6 @@
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>